--- a/business-libraries/test-data/self_growth/assessment.xlsx
+++ b/business-libraries/test-data/self_growth/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:Q3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,91 +419,40 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>结果可见性*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>来源属性*</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>手册出处*</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>版本*</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
-      </c>
-      <c r="R1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="S1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="T1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="V1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="X1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AA1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>后续建议动作</v>
       </c>
     </row>
     <row r="2">
@@ -511,7 +460,7 @@
         <v>SG_FIVE_Q</v>
       </c>
       <c r="B2" t="str">
-        <v>自我成长赋能教师状态五问</v>
+        <v>班主任状态五问</v>
       </c>
       <c r="C2" t="str">
         <v>状态五问</v>
@@ -523,102 +472,51 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H2" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I2" t="str">
-        <v>self_report</v>
+        <v>monthly</v>
       </c>
       <c r="J2" t="str">
-        <v>manual</v>
+        <v>是</v>
       </c>
       <c r="K2" t="str">
-        <v>monthly</v>
+        <v>3</v>
       </c>
       <c r="L2" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M2" t="str">
-        <v>3</v>
+        <v>sensitive</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O2" t="str">
-        <v>5</v>
+        <v>自我成长赋能手册v1</v>
       </c>
       <c r="P2" t="str">
-        <v>每月一次</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q2" t="str">
-        <v>30</v>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U2" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V2" t="str">
-        <v>highly_sensitive</v>
-      </c>
-      <c r="W2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v>技术理论手册V5 第3章</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>回顾最近一周状态，产出多维评估结果</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>全国中小学班主任常模 N=3200</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>Cronbach α=0.87</v>
-      </c>
-      <c r="AD2" t="str">
-        <v>与GHQ-12 相关系数 r=0.64</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>数据仅用于教学支持，不用于人事考核</v>
-      </c>
-      <c r="AF2" t="str">
-        <v>适用于在职班主任，不适用于实习或代课教师</v>
-      </c>
-      <c r="AG2" t="str">
-        <v>教师正在经历重大个人变故时，建议先转介心理支持再施测</v>
-      </c>
-      <c r="AH2" t="str">
-        <v>如总分&gt;=17，建议进行深度访谈并启动个案</v>
+        <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B3" t="str">
-        <v>自我成长赋能教师压力与资源评估</v>
+        <v>教师心理资本与状态深度评估</v>
       </c>
       <c r="C3" t="str">
-        <v>压力资源</v>
+        <v>HERO深评</v>
       </c>
       <c r="D3" t="str">
         <v>self_growth</v>
@@ -627,103 +525,52 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>8</v>
       </c>
       <c r="L3" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M3" t="str">
-        <v>5</v>
+        <v>sensitive</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O3" t="str">
-        <v>8</v>
+        <v>自我成长赋能手册v1</v>
       </c>
       <c r="P3" t="str">
-        <v>学期初/学期末</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q3" t="str">
-        <v>90</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U3" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V3" t="str">
-        <v>internal</v>
-      </c>
-      <c r="W3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v>技术理论手册V5 第4章</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>评估教师在自我成长赋能相关维度的资源与压力状况</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>全国中小学班主任常模 N=2800</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>Cronbach α=0.82</v>
-      </c>
-      <c r="AD3" t="str">
-        <v>内容效度经专家评审</v>
-      </c>
-      <c r="AE3" t="str">
-        <v>数据仅用于教学支持</v>
-      </c>
-      <c r="AF3" t="str">
-        <v>适用于在职班主任</v>
-      </c>
-      <c r="AG3" t="str">
-        <v>教师在严重心理危机时，建议先进行心理评估</v>
-      </c>
-      <c r="AH3" t="str">
-        <v>根据评估结果推荐相应的支持工具</v>
+        <v>基于 HERO 心理资本框架，用于状态五问提示需支持后的深度评估。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:J14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -739,40 +586,22 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
@@ -786,43 +615,25 @@
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>EMOTION</v>
+        <v>情绪状态</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>这一周，我有多少时间感到身心疲惫、难以恢复？</v>
       </c>
       <c r="F2" t="str">
-        <v>这一周，我有多少时间感到最近一周的情绪耗竭程度？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H2" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
         <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -836,43 +647,25 @@
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>BOUNDARY</v>
+        <v>角色边界</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>这一周，我有多少次感到「什么都是我的责任」？</v>
       </c>
       <c r="F3" t="str">
-        <v>这一周，我有多少时间感到角色边界模糊程度？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H3" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
         <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -886,43 +679,25 @@
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>MEANING</v>
+        <v>意义感知</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>这一周，有多少次我觉得「当班主任是值得的」？</v>
       </c>
       <c r="F4" t="str">
-        <v>这一周，我有多少时间感到对工作意义的感知水平？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H4" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
         <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -936,43 +711,25 @@
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>EFFICACY</v>
+        <v>效能信心</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>遇到让我头疼的学生或家长问题时，我对自己能处理好多有信心？</v>
       </c>
       <c r="F5" t="str">
-        <v>这一周，我有多少时间感到面对困难时的自我效能？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H5" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
         <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -986,305 +743,293 @@
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>SUPPORT</v>
+        <v>同伴支持</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>这一周，我有多少时间感到工作中的困难没有人可以分担？</v>
       </c>
       <c r="F6" t="str">
-        <v>这一周，我有多少时间感到感受到的同伴和管理层支持？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H6" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
         <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B7" t="str">
-        <v>q1</v>
+        <v>h1</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>EMOTION</v>
+        <v>希望</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>面对当前的班级难题，我能想出不止一条可行的解决路径。</v>
       </c>
       <c r="F7" t="str">
-        <v>在自我成长赋能方面，评估教师最近一周的情绪耗竭程度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H7" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
         <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B8" t="str">
-        <v>q2</v>
+        <v>h2</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>BOUNDARY</v>
+        <v>希望</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>我对这个学期想达成的目标有清晰的推进计划。</v>
       </c>
       <c r="F8" t="str">
-        <v>在自我成长赋能方面，评估教师角色边界模糊程度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H8" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
         <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B9" t="str">
-        <v>q3</v>
+        <v>e1</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>MEANING</v>
+        <v>效能信心</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>即使遇到从未处理过的家校冲突，我也相信自己能处理好。</v>
       </c>
       <c r="F9" t="str">
-        <v>在自我成长赋能方面，评估教师对工作意义的感知水平的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H9" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
         <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B10" t="str">
-        <v>q4</v>
+        <v>e2</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>EFFICACY</v>
+        <v>效能信心</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>我有信心影响班上最难带的那几个学生。</v>
       </c>
       <c r="F10" t="str">
-        <v>在自我成长赋能方面，评估教师面对困难时的自我效能的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H10" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
         <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B11" t="str">
-        <v>q5</v>
+        <v>r1</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>SUPPORT</v>
+        <v>韧性</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>被家长质疑或投诉后，我能较快恢复工作状态。</v>
       </c>
       <c r="F11" t="str">
-        <v>在自我成长赋能方面，评估教师感受到的同伴和管理层支持的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H11" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
         <v>compute</v>
       </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v>5</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="B12" t="str">
+        <v>r2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>single</v>
+      </c>
+      <c r="D12" t="str">
+        <v>韧性</v>
+      </c>
+      <c r="E12" t="str">
+        <v>工作中的挫折不会长时间影响我的生活。</v>
+      </c>
+      <c r="F12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G12" t="str">
+        <v>是</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
+        <v>是</v>
+      </c>
+      <c r="J12" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="B13" t="str">
+        <v>o1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>single</v>
+      </c>
+      <c r="D13" t="str">
+        <v>乐观</v>
+      </c>
+      <c r="E13" t="str">
+        <v>我倾向于相信班级的情况会慢慢变好。</v>
+      </c>
+      <c r="F13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G13" t="str">
+        <v>是</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
+        <v>是</v>
+      </c>
+      <c r="J13" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SG_HERO_AS</v>
+      </c>
+      <c r="B14" t="str">
+        <v>o2</v>
+      </c>
+      <c r="C14" t="str">
+        <v>single</v>
+      </c>
+      <c r="D14" t="str">
+        <v>乐观</v>
+      </c>
+      <c r="E14" t="str">
+        <v>遇到问题时，我更多想到的是机会而不是麻烦。</v>
+      </c>
+      <c r="F14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G14" t="str">
+        <v>是</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
+        <v>是</v>
+      </c>
+      <c r="J14" t="str">
+        <v>compute</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1370,16 +1115,86 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:I10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1409,19 +1224,13 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>SG_FIVE_Q</v>
       </c>
       <c r="B2" t="str">
-        <v>EMOTION</v>
+        <v>SG_EMOTION</v>
       </c>
       <c r="C2" t="str">
         <v>情绪状态</v>
@@ -1436,19 +1245,13 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>评估教师最近一周的情绪耗竭程度</v>
+        <v>情绪状态维度</v>
       </c>
       <c r="H2" t="str">
-        <v>&gt;=4 分：情绪耗竭风险高，可能伴随躯体症状</v>
+        <v>情绪耗竭风险高，可能伴随躯体症状</v>
       </c>
       <c r="I2" t="str">
-        <v>&lt;=2 分：情绪状态良好，具备较好的自我调节能力</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="K2" t="str">
-        <v>0.9</v>
+        <v>情绪状态良好，具备较好的自我调节能力</v>
       </c>
     </row>
     <row r="3">
@@ -1456,7 +1259,7 @@
         <v>SG_FIVE_Q</v>
       </c>
       <c r="B3" t="str">
-        <v>BOUNDARY</v>
+        <v>SG_BOUNDARY</v>
       </c>
       <c r="C3" t="str">
         <v>角色边界</v>
@@ -1471,19 +1274,13 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>评估教师角色边界模糊程度</v>
+        <v>角色边界维度</v>
       </c>
       <c r="H3" t="str">
-        <v>&gt;=4 分：角色边界严重模糊</v>
+        <v>责任边界模糊，倾向于独自承接全部问题</v>
       </c>
       <c r="I3" t="str">
-        <v>&lt;=2 分：角色边界清晰</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2.5</v>
-      </c>
-      <c r="K3" t="str">
-        <v>0.8</v>
+        <v>职责边界清晰</v>
       </c>
     </row>
     <row r="4">
@@ -1491,7 +1288,7 @@
         <v>SG_FIVE_Q</v>
       </c>
       <c r="B4" t="str">
-        <v>MEANING</v>
+        <v>SG_MEANING</v>
       </c>
       <c r="C4" t="str">
         <v>意义感知</v>
@@ -1506,19 +1303,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>评估教师对工作意义的感知水平</v>
+        <v>意义感知维度</v>
       </c>
       <c r="H4" t="str">
-        <v>&gt;=4 分：意义感强烈</v>
+        <v>意义感流失，需重点关注</v>
       </c>
       <c r="I4" t="str">
-        <v>&lt;=2 分：意义感低下</v>
-      </c>
-      <c r="J4" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="K4" t="str">
-        <v>0.7</v>
+        <v>意义感充足</v>
       </c>
     </row>
     <row r="5">
@@ -1526,7 +1317,7 @@
         <v>SG_FIVE_Q</v>
       </c>
       <c r="B5" t="str">
-        <v>EFFICACY</v>
+        <v>SG_EFFICACY</v>
       </c>
       <c r="C5" t="str">
         <v>效能信心</v>
@@ -1541,19 +1332,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>评估教师面对困难时的自我效能</v>
+        <v>效能信心维度</v>
       </c>
       <c r="H5" t="str">
-        <v>&gt;=4 分：效能感强</v>
+        <v>对处理复杂问题缺乏信心</v>
       </c>
       <c r="I5" t="str">
-        <v>&lt;=2 分：效能感不足</v>
-      </c>
-      <c r="J5" t="str">
-        <v>3.0</v>
-      </c>
-      <c r="K5" t="str">
-        <v>0.8</v>
+        <v>效能感稳定</v>
       </c>
     </row>
     <row r="6">
@@ -1561,10 +1346,10 @@
         <v>SG_FIVE_Q</v>
       </c>
       <c r="B6" t="str">
-        <v>SUPPORT</v>
+        <v>SG_SUPPORT</v>
       </c>
       <c r="C6" t="str">
-        <v>支持感知</v>
+        <v>同伴支持</v>
       </c>
       <c r="D6" t="str">
         <v>q5</v>
@@ -1576,33 +1361,27 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>评估教师感受到的同伴和管理层支持</v>
+        <v>同伴支持维度</v>
       </c>
       <c r="H6" t="str">
-        <v>&gt;=4 分：支持感知良好</v>
+        <v>困难长期无人分担</v>
       </c>
       <c r="I6" t="str">
-        <v>&lt;=2 分：支持感知不足</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2.9</v>
-      </c>
-      <c r="K6" t="str">
-        <v>0.85</v>
+        <v>有稳定的支持来源</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B7" t="str">
-        <v>EMOTION</v>
+        <v>SG_HOPE</v>
       </c>
       <c r="C7" t="str">
-        <v>情绪状态</v>
+        <v>希望</v>
       </c>
       <c r="D7" t="str">
-        <v>q1</v>
+        <v>h1,h2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1611,33 +1390,27 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>评估教师最近一周的情绪耗竭程度</v>
+        <v>希望维度</v>
       </c>
       <c r="H7" t="str">
-        <v>&gt;=4 分：情绪耗竭风险高，可能伴随躯体症状</v>
+        <v>对目标路径有清晰规划</v>
       </c>
       <c r="I7" t="str">
-        <v>&lt;=2 分：情绪状态良好，具备较好的自我调节能力</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="K7" t="str">
-        <v>0.9</v>
+        <v>看不到可行路径</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B8" t="str">
-        <v>BOUNDARY</v>
+        <v>SG_EFFICACY</v>
       </c>
       <c r="C8" t="str">
-        <v>角色边界</v>
+        <v>效能信心</v>
       </c>
       <c r="D8" t="str">
-        <v>q2</v>
+        <v>e1,e2</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -1646,33 +1419,27 @@
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>评估教师角色边界模糊程度</v>
+        <v>效能信心维度</v>
       </c>
       <c r="H8" t="str">
-        <v>&gt;=4 分：角色边界严重模糊</v>
+        <v>相信自己能应对挑战</v>
       </c>
       <c r="I8" t="str">
-        <v>&lt;=2 分：角色边界清晰</v>
-      </c>
-      <c r="J8" t="str">
-        <v>2.5</v>
-      </c>
-      <c r="K8" t="str">
-        <v>0.8</v>
+        <v>对自身能力持续怀疑</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B9" t="str">
-        <v>MEANING</v>
+        <v>SG_RESILIENCE</v>
       </c>
       <c r="C9" t="str">
-        <v>意义感知</v>
+        <v>韧性</v>
       </c>
       <c r="D9" t="str">
-        <v>q3</v>
+        <v>r1,r2</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -1681,33 +1448,27 @@
         <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v>评估教师对工作意义的感知水平</v>
+        <v>韧性维度</v>
       </c>
       <c r="H9" t="str">
-        <v>&gt;=4 分：意义感强烈</v>
+        <v>受挫后能较快恢复</v>
       </c>
       <c r="I9" t="str">
-        <v>&lt;=2 分：意义感低下</v>
-      </c>
-      <c r="J9" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="K9" t="str">
-        <v>0.7</v>
+        <v>受挫后长时间难以恢复</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_QUICK</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B10" t="str">
-        <v>EFFICACY</v>
+        <v>SG_OPTIMISM</v>
       </c>
       <c r="C10" t="str">
-        <v>效能信心</v>
+        <v>乐观</v>
       </c>
       <c r="D10" t="str">
-        <v>q4</v>
+        <v>o1,o2</v>
       </c>
       <c r="E10" t="str">
         <v>mean</v>
@@ -1716,59 +1477,18 @@
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>评估教师面对困难时的自我效能</v>
+        <v>乐观维度</v>
       </c>
       <c r="H10" t="str">
-        <v>&gt;=4 分：效能感强</v>
+        <v>对未来持积极预期</v>
       </c>
       <c r="I10" t="str">
-        <v>&lt;=2 分：效能感不足</v>
-      </c>
-      <c r="J10" t="str">
-        <v>3.0</v>
-      </c>
-      <c r="K10" t="str">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>SG_QUICK</v>
-      </c>
-      <c r="B11" t="str">
-        <v>SUPPORT</v>
-      </c>
-      <c r="C11" t="str">
-        <v>支持感知</v>
-      </c>
-      <c r="D11" t="str">
-        <v>q5</v>
-      </c>
-      <c r="E11" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F11" t="str">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
-        <v>评估教师感受到的同伴和管理层支持</v>
-      </c>
-      <c r="H11" t="str">
-        <v>&gt;=4 分：支持感知良好</v>
-      </c>
-      <c r="I11" t="str">
-        <v>&lt;=2 分：支持感知不足</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2.9</v>
-      </c>
-      <c r="K11" t="str">
-        <v>0.85</v>
+        <v>倾向于预期负面结果</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/self_growth/assessment.xlsx
+++ b/business-libraries/test-data/self_growth/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,21 +437,36 @@
         <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
+        <v>量表角色*</v>
+      </c>
+      <c r="M1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="O1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="P1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="Q1" t="str">
         <v>结果可见性*</v>
       </c>
-      <c r="M1" t="str">
+      <c r="R1" t="str">
         <v>数据敏感级*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="S1" t="str">
         <v>来源属性*</v>
       </c>
-      <c r="O1" t="str">
+      <c r="T1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="U1" t="str">
         <v>版本*</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="V1" t="str">
         <v>量表说明</v>
       </c>
     </row>
@@ -490,21 +505,36 @@
         <v>3</v>
       </c>
       <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M2" t="str">
+      <c r="R2" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N2" t="str">
+      <c r="S2" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O2" t="str">
+      <c r="T2" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
-      <c r="P2" t="str">
+      <c r="U2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="V2" t="str">
         <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
       </c>
     </row>
@@ -543,27 +573,42 @@
         <v>8</v>
       </c>
       <c r="L3" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="M3" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>量表[SG_FIVE_Q].总分 &gt;= 17</v>
+      </c>
+      <c r="P3" t="str">
+        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
+      </c>
+      <c r="Q3" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M3" t="str">
+      <c r="R3" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N3" t="str">
+      <c r="S3" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O3" t="str">
+      <c r="T3" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
-      <c r="P3" t="str">
+      <c r="U3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="V3" t="str">
         <v>基于 HERO 心理资本框架，用于状态五问提示需支持后的深度评估。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/self_growth/assessment.xlsx
+++ b/business-libraries/test-data/self_growth/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,55 +419,103 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
@@ -487,55 +535,103 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>monthly</v>
       </c>
-      <c r="J2" t="str">
-        <v>是</v>
-      </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
+        <v>是</v>
+      </c>
+      <c r="M2" t="str">
         <v>3</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
+      <c r="AL2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -555,67 +651,115 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>8</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>SG_FIVE_Q</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[SG_FIVE_Q].总分 &gt;= 17</v>
+      </c>
+      <c r="U3" t="str">
+        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>基于 HERO 心理资本框架，用于状态五问提示需支持后的深度评估。</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>SG_FIVE_Q</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[SG_FIVE_Q].总分 &gt;= 17</v>
-      </c>
-      <c r="P3" t="str">
-        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T3" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>基于 HERO 心理资本框架，用于状态五问提示需支持后的深度评估。</v>
+      <c r="AL3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:P14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,22 +775,40 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
@@ -663,22 +825,40 @@
         <v>情绪状态</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>这一周，我有多少时间感到身心疲惫、难以恢复？</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>否</v>
       </c>
-      <c r="H2" t="str">
-        <v>1</v>
-      </c>
-      <c r="I2" t="str">
-        <v>是</v>
-      </c>
       <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>是</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -695,22 +875,40 @@
         <v>角色边界</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>这一周，我有多少次感到「什么都是我的责任」？</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>否</v>
       </c>
-      <c r="H3" t="str">
-        <v>1</v>
-      </c>
-      <c r="I3" t="str">
-        <v>是</v>
-      </c>
       <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>是</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -727,22 +925,40 @@
         <v>意义感知</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>这一周，有多少次我觉得「当班主任是值得的」？</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G4" t="str">
-        <v>是</v>
-      </c>
-      <c r="H4" t="str">
-        <v>1</v>
-      </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>是</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -759,22 +975,40 @@
         <v>效能信心</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>遇到让我头疼的学生或家长问题时，我对自己能处理好多有信心？</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G5" t="str">
-        <v>是</v>
-      </c>
-      <c r="H5" t="str">
-        <v>1</v>
-      </c>
       <c r="I5" t="str">
         <v>是</v>
       </c>
       <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>是</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -791,22 +1025,40 @@
         <v>同伴支持</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>这一周，我有多少时间感到工作中的困难没有人可以分担？</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>否</v>
       </c>
-      <c r="H6" t="str">
-        <v>1</v>
-      </c>
-      <c r="I6" t="str">
-        <v>是</v>
-      </c>
       <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>是</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -823,22 +1075,40 @@
         <v>希望</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>面对当前的班级难题，我能想出不止一条可行的解决路径。</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G7" t="str">
-        <v>是</v>
-      </c>
-      <c r="H7" t="str">
-        <v>1</v>
-      </c>
       <c r="I7" t="str">
         <v>是</v>
       </c>
       <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>是</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -855,22 +1125,40 @@
         <v>希望</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>我对这个学期想达成的目标有清晰的推进计划。</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G8" t="str">
-        <v>是</v>
-      </c>
-      <c r="H8" t="str">
-        <v>1</v>
-      </c>
       <c r="I8" t="str">
         <v>是</v>
       </c>
       <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>是</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -887,22 +1175,40 @@
         <v>效能信心</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>即使遇到从未处理过的家校冲突，我也相信自己能处理好。</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G9" t="str">
-        <v>是</v>
-      </c>
-      <c r="H9" t="str">
-        <v>1</v>
-      </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>是</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -919,22 +1225,40 @@
         <v>效能信心</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>我有信心影响班上最难带的那几个学生。</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G10" t="str">
-        <v>是</v>
-      </c>
-      <c r="H10" t="str">
-        <v>1</v>
-      </c>
       <c r="I10" t="str">
         <v>是</v>
       </c>
       <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>是</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -951,22 +1275,40 @@
         <v>韧性</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>被家长质疑或投诉后，我能较快恢复工作状态。</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G11" t="str">
-        <v>是</v>
-      </c>
-      <c r="H11" t="str">
-        <v>1</v>
-      </c>
       <c r="I11" t="str">
         <v>是</v>
       </c>
       <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>是</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -983,22 +1325,40 @@
         <v>韧性</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>工作中的挫折不会长时间影响我的生活。</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G12" t="str">
-        <v>是</v>
-      </c>
-      <c r="H12" t="str">
-        <v>1</v>
-      </c>
       <c r="I12" t="str">
         <v>是</v>
       </c>
       <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>是</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1015,22 +1375,40 @@
         <v>乐观</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>我倾向于相信班级的情况会慢慢变好。</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G13" t="str">
-        <v>是</v>
-      </c>
-      <c r="H13" t="str">
-        <v>1</v>
-      </c>
       <c r="I13" t="str">
         <v>是</v>
       </c>
       <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>是</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1047,27 +1425,45 @@
         <v>乐观</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>遇到问题时，我更多想到的是机会而不是麻烦。</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G14" t="str">
-        <v>是</v>
-      </c>
-      <c r="H14" t="str">
-        <v>1</v>
-      </c>
       <c r="I14" t="str">
         <v>是</v>
       </c>
       <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>是</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1239,7 +1635,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1269,6 +1665,12 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1298,6 +1700,12 @@
       <c r="I2" t="str">
         <v>情绪状态良好，具备较好的自我调节能力</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1327,6 +1735,12 @@
       <c r="I3" t="str">
         <v>职责边界清晰</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1356,6 +1770,12 @@
       <c r="I4" t="str">
         <v>意义感充足</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1385,6 +1805,12 @@
       <c r="I5" t="str">
         <v>效能感稳定</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1414,6 +1840,12 @@
       <c r="I6" t="str">
         <v>有稳定的支持来源</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1443,6 +1875,12 @@
       <c r="I7" t="str">
         <v>看不到可行路径</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1472,6 +1910,12 @@
       <c r="I8" t="str">
         <v>对自身能力持续怀疑</v>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1501,6 +1945,12 @@
       <c r="I9" t="str">
         <v>受挫后长时间难以恢复</v>
       </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1530,10 +1980,16 @@
       <c r="I10" t="str">
         <v>倾向于预期负面结果</v>
       </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/self_growth/assessment.xlsx
+++ b/business-libraries/test-data/self_growth/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -520,7 +520,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B2" t="str">
         <v>班主任状态五问</v>
@@ -586,7 +586,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W2" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X2" t="str">
         <v>sensitive</v>
@@ -601,7 +601,7 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AB2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC2" t="str">
         <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
@@ -631,12 +631,12 @@
         <v>入口筛查</v>
       </c>
       <c r="AL2" t="str">
-        <v/>
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B3" t="str">
         <v>教师心理资本与状态深度评估</v>
@@ -687,13 +687,13 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="S3" t="str">
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[SG_FIVE_Q].总分 &gt;= 17</v>
+        <v>量表[SG_S1].总分 &gt;= 17</v>
       </c>
       <c r="U3" t="str">
         <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
@@ -702,7 +702,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W3" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X3" t="str">
         <v>sensitive</v>
@@ -717,10 +717,10 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AB3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>基于 HERO 心理资本框架，用于状态五问提示需支持后的深度评估。</v>
+        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -747,19 +747,135 @@
         <v>深度诊断</v>
       </c>
       <c r="AL3" t="str">
-        <v/>
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>教师危机风险自查</v>
+      </c>
+      <c r="C4" t="str">
+        <v>教师危机风险自查</v>
+      </c>
+      <c r="D4" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="E4" t="str">
+        <v>all</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I4" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="J4" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K4" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="L4" t="str">
+        <v>否</v>
+      </c>
+      <c r="M4" t="str">
+        <v>3</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>量表[SG_S1].总分 &gt;= 17</v>
+      </c>
+      <c r="U4" t="str">
+        <v>状态五问总分达到 17 分及以上时，建议做一次危机风险自查</v>
+      </c>
+      <c r="V4" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W4" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X4" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>状态五问总分达到需支持档位后，逐项自查高危信号，勾选频率越高越需要立即干预。</v>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+      <c r="AK4" t="str">
+        <v>红线检查</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -813,7 +929,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B2" t="str">
         <v>q1</v>
@@ -863,7 +979,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B3" t="str">
         <v>q2</v>
@@ -913,7 +1029,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B4" t="str">
         <v>q3</v>
@@ -934,7 +1050,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>FREQ_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
@@ -963,7 +1079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B5" t="str">
         <v>q4</v>
@@ -1013,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B6" t="str">
         <v>q5</v>
@@ -1063,10 +1179,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>h1</v>
+        <v>q1</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -1113,10 +1229,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>h2</v>
+        <v>q2</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -1163,10 +1279,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B9" t="str">
-        <v>e1</v>
+        <v>q3</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -1213,10 +1329,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B10" t="str">
-        <v>e2</v>
+        <v>q4</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -1263,10 +1379,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B11" t="str">
-        <v>r1</v>
+        <v>q5</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -1313,10 +1429,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B12" t="str">
-        <v>r2</v>
+        <v>q6</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -1363,10 +1479,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B13" t="str">
-        <v>o1</v>
+        <v>q7</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1413,10 +1529,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B14" t="str">
-        <v>o2</v>
+        <v>q8</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1461,16 +1577,316 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>single</v>
+      </c>
+      <c r="D15" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>最近一周，入睡困难或早醒的情况有多频繁？</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I15" t="str">
+        <v>否</v>
+      </c>
+      <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>是</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B16" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>single</v>
+      </c>
+      <c r="D16" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>最近一周，上班前感到难以承受、不想面对工作的频率？</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I16" t="str">
+        <v>否</v>
+      </c>
+      <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>是</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B17" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>single</v>
+      </c>
+      <c r="D17" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>最近一周，出现情绪失控或想对身边人发火的次数？</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I17" t="str">
+        <v>否</v>
+      </c>
+      <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>是</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B18" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C18" t="str">
+        <v>single</v>
+      </c>
+      <c r="D18" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>最近一周，注意力无法集中、做事丢三落四的频率？</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I18" t="str">
+        <v>否</v>
+      </c>
+      <c r="J18" t="str">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>是</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C19" t="str">
+        <v>single</v>
+      </c>
+      <c r="D19" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>最近一周，对工作完全提不起兴趣的频率？</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I19" t="str">
+        <v>否</v>
+      </c>
+      <c r="J19" t="str">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>是</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B20" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C20" t="str">
+        <v>single</v>
+      </c>
+      <c r="D20" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>最近一周，是否出现过伤害自己的念头？</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I20" t="str">
+        <v>否</v>
+      </c>
+      <c r="J20" t="str">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>是</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1558,13 +1974,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B7" t="str">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>完全不符合</v>
+        <v>完全没有</v>
       </c>
       <c r="D7" t="str">
         <v>1</v>
@@ -1572,13 +1988,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B8" t="str">
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>比较不符合</v>
+        <v>偶尔有</v>
       </c>
       <c r="D8" t="str">
         <v>2</v>
@@ -1586,13 +2002,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B9" t="str">
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>一般</v>
+        <v>有时有</v>
       </c>
       <c r="D9" t="str">
         <v>3</v>
@@ -1600,13 +2016,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B10" t="str">
         <v>4</v>
       </c>
       <c r="C10" t="str">
-        <v>比较符合</v>
+        <v>经常有</v>
       </c>
       <c r="D10" t="str">
         <v>4</v>
@@ -1614,28 +2030,98 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B11" t="str">
         <v>5</v>
       </c>
       <c r="C11" t="str">
-        <v>非常符合</v>
+        <v>几乎总是</v>
       </c>
       <c r="D11" t="str">
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B12" t="str">
+        <v>1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2</v>
+      </c>
+      <c r="C13" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B14" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D14" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B15" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D15" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>5</v>
+      </c>
+      <c r="C16" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D16" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1674,10 +2160,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>SG_EMOTION</v>
+        <v>SG_S1D1</v>
       </c>
       <c r="C2" t="str">
         <v>情绪状态</v>
@@ -1709,10 +2195,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>SG_BOUNDARY</v>
+        <v>SG_S1D2</v>
       </c>
       <c r="C3" t="str">
         <v>角色边界</v>
@@ -1744,10 +2230,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>SG_MEANING</v>
+        <v>SG_S1D3</v>
       </c>
       <c r="C4" t="str">
         <v>意义感知</v>
@@ -1779,10 +2265,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>SG_EFFICACY</v>
+        <v>SG_S1D4</v>
       </c>
       <c r="C5" t="str">
         <v>效能信心</v>
@@ -1814,10 +2300,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>SG_SUPPORT</v>
+        <v>SG_S1D5</v>
       </c>
       <c r="C6" t="str">
         <v>同伴支持</v>
@@ -1849,16 +2335,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>SG_HOPE</v>
+        <v>SG_S2D1</v>
       </c>
       <c r="C7" t="str">
         <v>希望</v>
       </c>
       <c r="D7" t="str">
-        <v>h1,h2</v>
+        <v>q1,q2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1884,16 +2370,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>SG_EFFICACY</v>
+        <v>SG_S2D2</v>
       </c>
       <c r="C8" t="str">
         <v>效能信心</v>
       </c>
       <c r="D8" t="str">
-        <v>e1,e2</v>
+        <v>q3,q4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -1919,16 +2405,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B9" t="str">
-        <v>SG_RESILIENCE</v>
+        <v>SG_S2D3</v>
       </c>
       <c r="C9" t="str">
         <v>韧性</v>
       </c>
       <c r="D9" t="str">
-        <v>r1,r2</v>
+        <v>q5,q6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -1954,16 +2440,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B10" t="str">
-        <v>SG_OPTIMISM</v>
+        <v>SG_S2D4</v>
       </c>
       <c r="C10" t="str">
         <v>乐观</v>
       </c>
       <c r="D10" t="str">
-        <v>o1,o2</v>
+        <v>q7,q8</v>
       </c>
       <c r="E10" t="str">
         <v>mean</v>
@@ -1987,9 +2473,44 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SG_S3D1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="D11" t="str">
+        <v>q1,q2,q3,q4,q5,q6</v>
+      </c>
+      <c r="E11" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/self_growth/assessment.xlsx
+++ b/business-libraries/test-data/self_growth/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL4"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,108 +419,60 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>量表角色*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>前置量表编码</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>互斥量表编码</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>触发条件</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>触发条件说明</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
+        <v>结果可见性*</v>
       </c>
       <c r="R1" t="str">
-        <v>前置量表编码</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="S1" t="str">
-        <v>互斥量表编码</v>
+        <v>来源属性*</v>
       </c>
       <c r="T1" t="str">
-        <v>触发条件</v>
+        <v>手册出处*</v>
       </c>
       <c r="U1" t="str">
-        <v>触发条件说明</v>
+        <v>版本*</v>
       </c>
       <c r="V1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="X1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AC1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>后续建议动作</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>量表角色*</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B2" t="str">
         <v>班主任状态五问</v>
@@ -535,28 +487,28 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="G2" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="H2" t="str">
+        <v>manual</v>
+      </c>
+      <c r="I2" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="J2" t="str">
+        <v>是</v>
+      </c>
+      <c r="K2" t="str">
+        <v>3</v>
+      </c>
+      <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
         <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v>teacher</v>
-      </c>
-      <c r="I2" t="str">
-        <v>self_report</v>
-      </c>
-      <c r="J2" t="str">
-        <v>manual</v>
-      </c>
-      <c r="K2" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="L2" t="str">
-        <v>是</v>
-      </c>
-      <c r="M2" t="str">
-        <v>3</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -568,75 +520,27 @@
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>teacher_only</v>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>sensitive</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>自我成长赋能手册v1</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>1.0.0</v>
       </c>
       <c r="V2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W2" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z2" t="str">
-        <v/>
-      </c>
-      <c r="AA2" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC2" t="str">
         <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
-      </c>
-      <c r="AD2" t="str">
-        <v/>
-      </c>
-      <c r="AE2" t="str">
-        <v/>
-      </c>
-      <c r="AF2" t="str">
-        <v/>
-      </c>
-      <c r="AG2" t="str">
-        <v/>
-      </c>
-      <c r="AH2" t="str">
-        <v/>
-      </c>
-      <c r="AI2" t="str">
-        <v/>
-      </c>
-      <c r="AJ2" t="str">
-        <v/>
-      </c>
-      <c r="AK2" t="str">
-        <v>入口筛查</v>
-      </c>
-      <c r="AL2" t="str">
-        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B3" t="str">
         <v>教师心理资本与状态深度评估</v>
@@ -651,231 +555,67 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>8</v>
       </c>
       <c r="L3" t="str">
-        <v>否</v>
+        <v>深度诊断</v>
       </c>
       <c r="M3" t="str">
-        <v>8</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>量表[SG_FIVE_Q].总分 &gt;= 17</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>teacher_only</v>
       </c>
       <c r="R3" t="str">
-        <v>SG_S1</v>
+        <v>sensitive</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="T3" t="str">
-        <v>量表[SG_S1].总分 &gt;= 17</v>
+        <v>自我成长赋能手册v1</v>
       </c>
       <c r="U3" t="str">
-        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
+        <v>1.0.0</v>
       </c>
       <c r="V3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W3" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z3" t="str">
-        <v/>
-      </c>
-      <c r="AA3" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
-      </c>
-      <c r="AD3" t="str">
-        <v/>
-      </c>
-      <c r="AE3" t="str">
-        <v/>
-      </c>
-      <c r="AF3" t="str">
-        <v/>
-      </c>
-      <c r="AG3" t="str">
-        <v/>
-      </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-      <c r="AI3" t="str">
-        <v/>
-      </c>
-      <c r="AJ3" t="str">
-        <v/>
-      </c>
-      <c r="AK3" t="str">
-        <v>深度诊断</v>
-      </c>
-      <c r="AL3" t="str">
-        <v>定位薄弱维度，匹配对应工具</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>教师危机风险自查</v>
-      </c>
-      <c r="C4" t="str">
-        <v>教师危机风险自查</v>
-      </c>
-      <c r="D4" t="str">
-        <v>self_growth</v>
-      </c>
-      <c r="E4" t="str">
-        <v>all</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>teacher</v>
-      </c>
-      <c r="I4" t="str">
-        <v>self_report</v>
-      </c>
-      <c r="J4" t="str">
-        <v>manual</v>
-      </c>
-      <c r="K4" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="L4" t="str">
-        <v>否</v>
-      </c>
-      <c r="M4" t="str">
-        <v>3</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v>SG_S1</v>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v>量表[SG_S1].总分 &gt;= 17</v>
-      </c>
-      <c r="U4" t="str">
-        <v>状态五问总分达到 17 分及以上时，建议做一次危机风险自查</v>
-      </c>
-      <c r="V4" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W4" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X4" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y4" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z4" t="str">
-        <v/>
-      </c>
-      <c r="AA4" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-      <c r="AB4" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC4" t="str">
-        <v>状态五问总分达到需支持档位后，逐项自查高危信号，勾选频率越高越需要立即干预。</v>
-      </c>
-      <c r="AD4" t="str">
-        <v/>
-      </c>
-      <c r="AE4" t="str">
-        <v/>
-      </c>
-      <c r="AF4" t="str">
-        <v/>
-      </c>
-      <c r="AG4" t="str">
-        <v/>
-      </c>
-      <c r="AH4" t="str">
-        <v/>
-      </c>
-      <c r="AI4" t="str">
-        <v/>
-      </c>
-      <c r="AJ4" t="str">
-        <v/>
-      </c>
-      <c r="AK4" t="str">
-        <v>红线检查</v>
-      </c>
-      <c r="AL4" t="str">
-        <v>定位薄弱维度，匹配对应工具</v>
+        <v>基于 HERO 心理资本框架，用于状态五问提示需支持后的深度评估。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -891,45 +631,27 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B2" t="str">
         <v>q1</v>
@@ -941,45 +663,27 @@
         <v>情绪状态</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>这一周，我有多少时间感到身心疲惫、难以恢复？</v>
       </c>
       <c r="F2" t="str">
-        <v>这一周，我有多少时间感到身心疲惫、难以恢复？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H2" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
         <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B3" t="str">
         <v>q2</v>
@@ -991,45 +695,27 @@
         <v>角色边界</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>这一周，我有多少次感到「什么都是我的责任」？</v>
       </c>
       <c r="F3" t="str">
-        <v>这一周，我有多少次感到「什么都是我的责任」？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H3" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
         <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B4" t="str">
         <v>q3</v>
@@ -1041,45 +727,27 @@
         <v>意义感知</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>这一周，有多少次我觉得「当班主任是值得的」？</v>
       </c>
       <c r="F4" t="str">
-        <v>这一周，有多少次我觉得「当班主任是值得的」？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H4" t="str">
-        <v>SG_OPT_01</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
         <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B5" t="str">
         <v>q4</v>
@@ -1091,45 +759,27 @@
         <v>效能信心</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>遇到让我头疼的学生或家长问题时，我对自己能处理好多有信心？</v>
       </c>
       <c r="F5" t="str">
-        <v>遇到让我头疼的学生或家长问题时，我对自己能处理好多有信心？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H5" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
         <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
         <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B6" t="str">
         <v>q5</v>
@@ -1141,48 +791,30 @@
         <v>同伴支持</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>这一周，我有多少时间感到工作中的困难没有人可以分担？</v>
       </c>
       <c r="F6" t="str">
-        <v>这一周，我有多少时间感到工作中的困难没有人可以分担？</v>
+        <v>FREQ_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H6" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
         <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B7" t="str">
-        <v>q1</v>
+        <v>h1</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -1191,48 +823,30 @@
         <v>希望</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>面对当前的班级难题，我能想出不止一条可行的解决路径。</v>
       </c>
       <c r="F7" t="str">
-        <v>面对当前的班级难题，我能想出不止一条可行的解决路径。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H7" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
         <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
         <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B8" t="str">
-        <v>q2</v>
+        <v>h2</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -1241,48 +855,30 @@
         <v>希望</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>我对这个学期想达成的目标有清晰的推进计划。</v>
       </c>
       <c r="F8" t="str">
-        <v>我对这个学期想达成的目标有清晰的推进计划。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H8" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
         <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B9" t="str">
-        <v>q3</v>
+        <v>e1</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -1291,48 +887,30 @@
         <v>效能信心</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>即使遇到从未处理过的家校冲突，我也相信自己能处理好。</v>
       </c>
       <c r="F9" t="str">
-        <v>即使遇到从未处理过的家校冲突，我也相信自己能处理好。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H9" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
         <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B10" t="str">
-        <v>q4</v>
+        <v>e2</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -1341,48 +919,30 @@
         <v>效能信心</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>我有信心影响班上最难带的那几个学生。</v>
       </c>
       <c r="F10" t="str">
-        <v>我有信心影响班上最难带的那几个学生。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H10" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
         <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
         <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B11" t="str">
-        <v>q5</v>
+        <v>r1</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -1391,48 +951,30 @@
         <v>韧性</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>被家长质疑或投诉后，我能较快恢复工作状态。</v>
       </c>
       <c r="F11" t="str">
-        <v>被家长质疑或投诉后，我能较快恢复工作状态。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H11" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
         <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
         <v>compute</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B12" t="str">
-        <v>q6</v>
+        <v>r2</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -1441,48 +983,30 @@
         <v>韧性</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>工作中的挫折不会长时间影响我的生活。</v>
       </c>
       <c r="F12" t="str">
-        <v>工作中的挫折不会长时间影响我的生活。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H12" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v>是</v>
       </c>
       <c r="J12" t="str">
-        <v>1</v>
-      </c>
-      <c r="K12" t="str">
-        <v>是</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
         <v>compute</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B13" t="str">
-        <v>q7</v>
+        <v>o1</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1491,48 +1015,30 @@
         <v>乐观</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>我倾向于相信班级的情况会慢慢变好。</v>
       </c>
       <c r="F13" t="str">
-        <v>我倾向于相信班级的情况会慢慢变好。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H13" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>是</v>
       </c>
       <c r="J13" t="str">
-        <v>1</v>
-      </c>
-      <c r="K13" t="str">
-        <v>是</v>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
         <v>compute</v>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B14" t="str">
-        <v>q8</v>
+        <v>o2</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1541,352 +1047,34 @@
         <v>乐观</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>遇到问题时，我更多想到的是机会而不是麻烦。</v>
       </c>
       <c r="F14" t="str">
-        <v>遇到问题时，我更多想到的是机会而不是麻烦。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H14" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
         <v>是</v>
       </c>
       <c r="J14" t="str">
-        <v>1</v>
-      </c>
-      <c r="K14" t="str">
-        <v>是</v>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
         <v>compute</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="B15" t="str">
-        <v>q1</v>
-      </c>
-      <c r="C15" t="str">
-        <v>single</v>
-      </c>
-      <c r="D15" t="str">
-        <v>高危信号</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v>最近一周，入睡困难或早醒的情况有多频繁？</v>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v>FREQ_5</v>
-      </c>
-      <c r="I15" t="str">
-        <v>否</v>
-      </c>
-      <c r="J15" t="str">
-        <v>1</v>
-      </c>
-      <c r="K15" t="str">
-        <v>是</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="B16" t="str">
-        <v>q2</v>
-      </c>
-      <c r="C16" t="str">
-        <v>single</v>
-      </c>
-      <c r="D16" t="str">
-        <v>高危信号</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v>最近一周，上班前感到难以承受、不想面对工作的频率？</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v>FREQ_5</v>
-      </c>
-      <c r="I16" t="str">
-        <v>否</v>
-      </c>
-      <c r="J16" t="str">
-        <v>1</v>
-      </c>
-      <c r="K16" t="str">
-        <v>是</v>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="B17" t="str">
-        <v>q3</v>
-      </c>
-      <c r="C17" t="str">
-        <v>single</v>
-      </c>
-      <c r="D17" t="str">
-        <v>高危信号</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v>最近一周，出现情绪失控或想对身边人发火的次数？</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v>FREQ_5</v>
-      </c>
-      <c r="I17" t="str">
-        <v>否</v>
-      </c>
-      <c r="J17" t="str">
-        <v>1</v>
-      </c>
-      <c r="K17" t="str">
-        <v>是</v>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="B18" t="str">
-        <v>q4</v>
-      </c>
-      <c r="C18" t="str">
-        <v>single</v>
-      </c>
-      <c r="D18" t="str">
-        <v>高危信号</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v>最近一周，注意力无法集中、做事丢三落四的频率？</v>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v>FREQ_5</v>
-      </c>
-      <c r="I18" t="str">
-        <v>否</v>
-      </c>
-      <c r="J18" t="str">
-        <v>1</v>
-      </c>
-      <c r="K18" t="str">
-        <v>是</v>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="B19" t="str">
-        <v>q5</v>
-      </c>
-      <c r="C19" t="str">
-        <v>single</v>
-      </c>
-      <c r="D19" t="str">
-        <v>高危信号</v>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v>最近一周，对工作完全提不起兴趣的频率？</v>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v>FREQ_5</v>
-      </c>
-      <c r="I19" t="str">
-        <v>否</v>
-      </c>
-      <c r="J19" t="str">
-        <v>1</v>
-      </c>
-      <c r="K19" t="str">
-        <v>是</v>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="B20" t="str">
-        <v>q6</v>
-      </c>
-      <c r="C20" t="str">
-        <v>single</v>
-      </c>
-      <c r="D20" t="str">
-        <v>高危信号</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v>最近一周，是否出现过伤害自己的念头？</v>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v>FREQ_5</v>
-      </c>
-      <c r="I20" t="str">
-        <v>否</v>
-      </c>
-      <c r="J20" t="str">
-        <v>1</v>
-      </c>
-      <c r="K20" t="str">
-        <v>是</v>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v>compute</v>
-      </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
-        <v/>
-      </c>
-      <c r="P20" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1974,13 +1162,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_OPT_01</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B7" t="str">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>完全没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D7" t="str">
         <v>1</v>
@@ -1988,13 +1176,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_OPT_01</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B8" t="str">
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>偶尔有</v>
+        <v>比较不符合</v>
       </c>
       <c r="D8" t="str">
         <v>2</v>
@@ -2002,13 +1190,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_OPT_01</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B9" t="str">
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>有时有</v>
+        <v>一般</v>
       </c>
       <c r="D9" t="str">
         <v>3</v>
@@ -2016,13 +1204,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_OPT_01</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B10" t="str">
         <v>4</v>
       </c>
       <c r="C10" t="str">
-        <v>经常有</v>
+        <v>比较符合</v>
       </c>
       <c r="D10" t="str">
         <v>4</v>
@@ -2030,98 +1218,28 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG_OPT_01</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B11" t="str">
         <v>5</v>
       </c>
       <c r="C11" t="str">
-        <v>几乎总是</v>
+        <v>非常符合</v>
       </c>
       <c r="D11" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B12" t="str">
-        <v>1</v>
-      </c>
-      <c r="C12" t="str">
-        <v>完全不符合</v>
-      </c>
-      <c r="D12" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2</v>
-      </c>
-      <c r="C13" t="str">
-        <v>比较不符合</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B14" t="str">
-        <v>3</v>
-      </c>
-      <c r="C14" t="str">
-        <v>一般</v>
-      </c>
-      <c r="D14" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B15" t="str">
-        <v>4</v>
-      </c>
-      <c r="C15" t="str">
-        <v>比较符合</v>
-      </c>
-      <c r="D15" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B16" t="str">
-        <v>5</v>
-      </c>
-      <c r="C16" t="str">
-        <v>非常符合</v>
-      </c>
-      <c r="D16" t="str">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:I10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2151,19 +1269,13 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B2" t="str">
-        <v>SG_S1D1</v>
+        <v>SG_EMOTION</v>
       </c>
       <c r="C2" t="str">
         <v>情绪状态</v>
@@ -2186,19 +1298,13 @@
       <c r="I2" t="str">
         <v>情绪状态良好，具备较好的自我调节能力</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B3" t="str">
-        <v>SG_S1D2</v>
+        <v>SG_BOUNDARY</v>
       </c>
       <c r="C3" t="str">
         <v>角色边界</v>
@@ -2221,19 +1327,13 @@
       <c r="I3" t="str">
         <v>职责边界清晰</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B4" t="str">
-        <v>SG_S1D3</v>
+        <v>SG_MEANING</v>
       </c>
       <c r="C4" t="str">
         <v>意义感知</v>
@@ -2256,19 +1356,13 @@
       <c r="I4" t="str">
         <v>意义感充足</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B5" t="str">
-        <v>SG_S1D4</v>
+        <v>SG_EFFICACY</v>
       </c>
       <c r="C5" t="str">
         <v>效能信心</v>
@@ -2291,19 +1385,13 @@
       <c r="I5" t="str">
         <v>效能感稳定</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_S1</v>
+        <v>SG_FIVE_Q</v>
       </c>
       <c r="B6" t="str">
-        <v>SG_S1D5</v>
+        <v>SG_SUPPORT</v>
       </c>
       <c r="C6" t="str">
         <v>同伴支持</v>
@@ -2326,25 +1414,19 @@
       <c r="I6" t="str">
         <v>有稳定的支持来源</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B7" t="str">
-        <v>SG_S2D1</v>
+        <v>SG_HOPE</v>
       </c>
       <c r="C7" t="str">
         <v>希望</v>
       </c>
       <c r="D7" t="str">
-        <v>q1,q2</v>
+        <v>h1,h2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -2361,25 +1443,19 @@
       <c r="I7" t="str">
         <v>看不到可行路径</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B8" t="str">
-        <v>SG_S2D2</v>
+        <v>SG_EFFICACY</v>
       </c>
       <c r="C8" t="str">
         <v>效能信心</v>
       </c>
       <c r="D8" t="str">
-        <v>q3,q4</v>
+        <v>e1,e2</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -2396,25 +1472,19 @@
       <c r="I8" t="str">
         <v>对自身能力持续怀疑</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B9" t="str">
-        <v>SG_S2D3</v>
+        <v>SG_RESILIENCE</v>
       </c>
       <c r="C9" t="str">
         <v>韧性</v>
       </c>
       <c r="D9" t="str">
-        <v>q5,q6</v>
+        <v>r1,r2</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -2431,25 +1501,19 @@
       <c r="I9" t="str">
         <v>受挫后长时间难以恢复</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_S2</v>
+        <v>SG_HERO_AS</v>
       </c>
       <c r="B10" t="str">
-        <v>SG_S2D4</v>
+        <v>SG_OPTIMISM</v>
       </c>
       <c r="C10" t="str">
         <v>乐观</v>
       </c>
       <c r="D10" t="str">
-        <v>q7,q8</v>
+        <v>o1,o2</v>
       </c>
       <c r="E10" t="str">
         <v>mean</v>
@@ -2466,51 +1530,10 @@
       <c r="I10" t="str">
         <v>倾向于预期负面结果</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>SG_S3</v>
-      </c>
-      <c r="B11" t="str">
-        <v>SG_S3D1</v>
-      </c>
-      <c r="C11" t="str">
-        <v>高危信号</v>
-      </c>
-      <c r="D11" t="str">
-        <v>q1,q2,q3,q4,q5,q6</v>
-      </c>
-      <c r="E11" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F11" t="str">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/self_growth/assessment.xlsx
+++ b/business-libraries/test-data/self_growth/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,60 +419,108 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B2" t="str">
         <v>班主任状态五问</v>
@@ -487,60 +535,108 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>monthly</v>
       </c>
-      <c r="J2" t="str">
-        <v>是</v>
-      </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
+        <v>是</v>
+      </c>
+      <c r="M2" t="str">
         <v>3</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>自我成长赋能手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
+      <c r="AL2" t="str">
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B3" t="str">
         <v>教师心理资本与状态深度评估</v>
@@ -555,67 +651,231 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>8</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[SG_S1].总分 &gt;= 17</v>
+      </c>
+      <c r="U3" t="str">
+        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>SG_FIVE_Q</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[SG_FIVE_Q].总分 &gt;= 17</v>
-      </c>
-      <c r="P3" t="str">
-        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
-      </c>
-      <c r="Q3" t="str">
+      <c r="AL3" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>教师危机风险自查</v>
+      </c>
+      <c r="C4" t="str">
+        <v>教师危机风险自查</v>
+      </c>
+      <c r="D4" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="E4" t="str">
+        <v>all</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I4" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="J4" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K4" t="str">
+        <v>monthly</v>
+      </c>
+      <c r="L4" t="str">
+        <v>否</v>
+      </c>
+      <c r="M4" t="str">
+        <v>3</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>SG_S1</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>量表[SG_S1].总分 &gt;= 17</v>
+      </c>
+      <c r="U4" t="str">
+        <v>状态五问总分达到 17 分及以上时，建议做一次危机风险自查</v>
+      </c>
+      <c r="V4" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="R3" t="str">
+      <c r="W4" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X4" t="str">
         <v>sensitive</v>
       </c>
-      <c r="S3" t="str">
+      <c r="Y4" t="str">
         <v>proprietary</v>
       </c>
-      <c r="T3" t="str">
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
         <v>自我成长赋能手册v1</v>
       </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>基于 HERO 心理资本框架，用于状态五问提示需支持后的深度评估。</v>
+      <c r="AB4" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>状态五问总分达到需支持档位后，逐项自查高危信号，勾选频率越高越需要立即干预。</v>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+      <c r="AK4" t="str">
+        <v>红线检查</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:P20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,27 +891,45 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B2" t="str">
         <v>q1</v>
@@ -663,27 +941,45 @@
         <v>情绪状态</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>这一周，我有多少时间感到身心疲惫、难以恢复？</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>否</v>
       </c>
-      <c r="H2" t="str">
-        <v>1</v>
-      </c>
-      <c r="I2" t="str">
-        <v>是</v>
-      </c>
       <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>是</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B3" t="str">
         <v>q2</v>
@@ -695,27 +991,45 @@
         <v>角色边界</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>这一周，我有多少次感到「什么都是我的责任」？</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>否</v>
       </c>
-      <c r="H3" t="str">
-        <v>1</v>
-      </c>
-      <c r="I3" t="str">
-        <v>是</v>
-      </c>
       <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>是</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B4" t="str">
         <v>q3</v>
@@ -727,27 +1041,45 @@
         <v>意义感知</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>这一周，有多少次我觉得「当班主任是值得的」？</v>
       </c>
-      <c r="F4" t="str">
-        <v>FREQ_5</v>
-      </c>
       <c r="G4" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>1</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>是</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B5" t="str">
         <v>q4</v>
@@ -759,27 +1091,45 @@
         <v>效能信心</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>遇到让我头疼的学生或家长问题时，我对自己能处理好多有信心？</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G5" t="str">
-        <v>是</v>
-      </c>
-      <c r="H5" t="str">
-        <v>1</v>
-      </c>
       <c r="I5" t="str">
         <v>是</v>
       </c>
       <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>是</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B6" t="str">
         <v>q5</v>
@@ -791,30 +1141,48 @@
         <v>同伴支持</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>这一周，我有多少时间感到工作中的困难没有人可以分担？</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>FREQ_5</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>否</v>
       </c>
-      <c r="H6" t="str">
-        <v>1</v>
-      </c>
-      <c r="I6" t="str">
-        <v>是</v>
-      </c>
       <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>是</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>h1</v>
+        <v>q1</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -823,30 +1191,48 @@
         <v>希望</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>面对当前的班级难题，我能想出不止一条可行的解决路径。</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G7" t="str">
-        <v>是</v>
-      </c>
-      <c r="H7" t="str">
-        <v>1</v>
-      </c>
       <c r="I7" t="str">
         <v>是</v>
       </c>
       <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>是</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>h2</v>
+        <v>q2</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -855,30 +1241,48 @@
         <v>希望</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>我对这个学期想达成的目标有清晰的推进计划。</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G8" t="str">
-        <v>是</v>
-      </c>
-      <c r="H8" t="str">
-        <v>1</v>
-      </c>
       <c r="I8" t="str">
         <v>是</v>
       </c>
       <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>是</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B9" t="str">
-        <v>e1</v>
+        <v>q3</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -887,30 +1291,48 @@
         <v>效能信心</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>即使遇到从未处理过的家校冲突，我也相信自己能处理好。</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G9" t="str">
-        <v>是</v>
-      </c>
-      <c r="H9" t="str">
-        <v>1</v>
-      </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>是</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B10" t="str">
-        <v>e2</v>
+        <v>q4</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -919,30 +1341,48 @@
         <v>效能信心</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>我有信心影响班上最难带的那几个学生。</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G10" t="str">
-        <v>是</v>
-      </c>
-      <c r="H10" t="str">
-        <v>1</v>
-      </c>
       <c r="I10" t="str">
         <v>是</v>
       </c>
       <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>是</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B11" t="str">
-        <v>r1</v>
+        <v>q5</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -951,30 +1391,48 @@
         <v>韧性</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>被家长质疑或投诉后，我能较快恢复工作状态。</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G11" t="str">
-        <v>是</v>
-      </c>
-      <c r="H11" t="str">
-        <v>1</v>
-      </c>
       <c r="I11" t="str">
         <v>是</v>
       </c>
       <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>是</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B12" t="str">
-        <v>r2</v>
+        <v>q6</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -983,30 +1441,48 @@
         <v>韧性</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>工作中的挫折不会长时间影响我的生活。</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G12" t="str">
-        <v>是</v>
-      </c>
-      <c r="H12" t="str">
-        <v>1</v>
-      </c>
       <c r="I12" t="str">
         <v>是</v>
       </c>
       <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>是</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B13" t="str">
-        <v>o1</v>
+        <v>q7</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1015,30 +1491,48 @@
         <v>乐观</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>我倾向于相信班级的情况会慢慢变好。</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G13" t="str">
-        <v>是</v>
-      </c>
-      <c r="H13" t="str">
-        <v>1</v>
-      </c>
       <c r="I13" t="str">
         <v>是</v>
       </c>
       <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>是</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B14" t="str">
-        <v>o2</v>
+        <v>q8</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1047,34 +1541,352 @@
         <v>乐观</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>遇到问题时，我更多想到的是机会而不是麻烦。</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G14" t="str">
-        <v>是</v>
-      </c>
-      <c r="H14" t="str">
-        <v>1</v>
-      </c>
       <c r="I14" t="str">
         <v>是</v>
       </c>
       <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>是</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>single</v>
+      </c>
+      <c r="D15" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>最近一周，入睡困难或早醒的情况有多频繁？</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I15" t="str">
+        <v>否</v>
+      </c>
+      <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>是</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B16" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>single</v>
+      </c>
+      <c r="D16" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>最近一周，上班前感到难以承受、不想面对工作的频率？</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I16" t="str">
+        <v>否</v>
+      </c>
+      <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>是</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B17" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>single</v>
+      </c>
+      <c r="D17" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>最近一周，出现情绪失控或想对身边人发火的次数？</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I17" t="str">
+        <v>否</v>
+      </c>
+      <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>是</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B18" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C18" t="str">
+        <v>single</v>
+      </c>
+      <c r="D18" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>最近一周，注意力无法集中、做事丢三落四的频率？</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I18" t="str">
+        <v>否</v>
+      </c>
+      <c r="J18" t="str">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>是</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C19" t="str">
+        <v>single</v>
+      </c>
+      <c r="D19" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>最近一周，对工作完全提不起兴趣的频率？</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I19" t="str">
+        <v>否</v>
+      </c>
+      <c r="J19" t="str">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>是</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B20" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C20" t="str">
+        <v>single</v>
+      </c>
+      <c r="D20" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>最近一周，是否出现过伤害自己的念头？</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I20" t="str">
+        <v>否</v>
+      </c>
+      <c r="J20" t="str">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>是</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1162,13 +1974,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B7" t="str">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>完全不符合</v>
+        <v>完全没有</v>
       </c>
       <c r="D7" t="str">
         <v>1</v>
@@ -1176,13 +1988,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B8" t="str">
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>比较不符合</v>
+        <v>偶尔有</v>
       </c>
       <c r="D8" t="str">
         <v>2</v>
@@ -1190,13 +2002,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B9" t="str">
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>一般</v>
+        <v>有时有</v>
       </c>
       <c r="D9" t="str">
         <v>3</v>
@@ -1204,13 +2016,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B10" t="str">
         <v>4</v>
       </c>
       <c r="C10" t="str">
-        <v>比较符合</v>
+        <v>经常有</v>
       </c>
       <c r="D10" t="str">
         <v>4</v>
@@ -1218,28 +2030,98 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>AGREE_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="B11" t="str">
         <v>5</v>
       </c>
       <c r="C11" t="str">
-        <v>非常符合</v>
+        <v>几乎总是</v>
       </c>
       <c r="D11" t="str">
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B12" t="str">
+        <v>1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D12" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2</v>
+      </c>
+      <c r="C13" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B14" t="str">
+        <v>3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D14" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B15" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D15" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>5</v>
+      </c>
+      <c r="C16" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D16" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1269,13 +2151,19 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>SG_EMOTION</v>
+        <v>SG_S1D1</v>
       </c>
       <c r="C2" t="str">
         <v>情绪状态</v>
@@ -1298,13 +2186,19 @@
       <c r="I2" t="str">
         <v>情绪状态良好，具备较好的自我调节能力</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>SG_BOUNDARY</v>
+        <v>SG_S1D2</v>
       </c>
       <c r="C3" t="str">
         <v>角色边界</v>
@@ -1327,13 +2221,19 @@
       <c r="I3" t="str">
         <v>职责边界清晰</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>SG_MEANING</v>
+        <v>SG_S1D3</v>
       </c>
       <c r="C4" t="str">
         <v>意义感知</v>
@@ -1356,13 +2256,19 @@
       <c r="I4" t="str">
         <v>意义感充足</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>SG_EFFICACY</v>
+        <v>SG_S1D4</v>
       </c>
       <c r="C5" t="str">
         <v>效能信心</v>
@@ -1385,13 +2291,19 @@
       <c r="I5" t="str">
         <v>效能感稳定</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_FIVE_Q</v>
+        <v>SG_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>SG_SUPPORT</v>
+        <v>SG_S1D5</v>
       </c>
       <c r="C6" t="str">
         <v>同伴支持</v>
@@ -1414,19 +2326,25 @@
       <c r="I6" t="str">
         <v>有稳定的支持来源</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>SG_HOPE</v>
+        <v>SG_S2D1</v>
       </c>
       <c r="C7" t="str">
         <v>希望</v>
       </c>
       <c r="D7" t="str">
-        <v>h1,h2</v>
+        <v>q1,q2</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1443,19 +2361,25 @@
       <c r="I7" t="str">
         <v>看不到可行路径</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B8" t="str">
-        <v>SG_EFFICACY</v>
+        <v>SG_S2D2</v>
       </c>
       <c r="C8" t="str">
         <v>效能信心</v>
       </c>
       <c r="D8" t="str">
-        <v>e1,e2</v>
+        <v>q3,q4</v>
       </c>
       <c r="E8" t="str">
         <v>mean</v>
@@ -1472,19 +2396,25 @@
       <c r="I8" t="str">
         <v>对自身能力持续怀疑</v>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B9" t="str">
-        <v>SG_RESILIENCE</v>
+        <v>SG_S2D3</v>
       </c>
       <c r="C9" t="str">
         <v>韧性</v>
       </c>
       <c r="D9" t="str">
-        <v>r1,r2</v>
+        <v>q5,q6</v>
       </c>
       <c r="E9" t="str">
         <v>mean</v>
@@ -1501,19 +2431,25 @@
       <c r="I9" t="str">
         <v>受挫后长时间难以恢复</v>
       </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_HERO_AS</v>
+        <v>SG_S2</v>
       </c>
       <c r="B10" t="str">
-        <v>SG_OPTIMISM</v>
+        <v>SG_S2D4</v>
       </c>
       <c r="C10" t="str">
         <v>乐观</v>
       </c>
       <c r="D10" t="str">
-        <v>o1,o2</v>
+        <v>q7,q8</v>
       </c>
       <c r="E10" t="str">
         <v>mean</v>
@@ -1530,10 +2466,51 @@
       <c r="I10" t="str">
         <v>倾向于预期负面结果</v>
       </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SG_S3D1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>高危信号</v>
+      </c>
+      <c r="D11" t="str">
+        <v>q1,q2,q3,q4,q5,q6</v>
+      </c>
+      <c r="E11" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/self_growth/assessment.xlsx
+++ b/business-libraries/test-data/self_growth/assessment.xlsx
@@ -523,10 +523,10 @@
         <v>SG_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>班主任状态五问</v>
+        <v>教师自我成长五问自评</v>
       </c>
       <c r="C2" t="str">
-        <v>状态五问</v>
+        <v>五问自评</v>
       </c>
       <c r="D2" t="str">
         <v>self_growth</v>
@@ -598,13 +598,13 @@
         <v/>
       </c>
       <c r="AA2" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB2" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC2" t="str">
-        <v>回顾最近一周的真实状态，3 分钟完成，系统按六色给出提示。</v>
+        <v>回顾最近一周的真实状态，3 分钟完成，系统按六色预警给出提示。总分越高越需关注；Q3、Q4 为保护性题目需反向计分。</v>
       </c>
       <c r="AD2" t="str">
         <v/>
@@ -639,10 +639,10 @@
         <v>SG_S2</v>
       </c>
       <c r="B3" t="str">
-        <v>教师心理资本与状态深度评估</v>
+        <v>HERO心理资本与依恋安全感评估</v>
       </c>
       <c r="C3" t="str">
-        <v>HERO深评</v>
+        <v>HERO+AS+PCS</v>
       </c>
       <c r="D3" t="str">
         <v>self_growth</v>
@@ -666,13 +666,13 @@
         <v>manual</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>monthly</v>
       </c>
       <c r="L3" t="str">
         <v>否</v>
       </c>
       <c r="M3" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[SG_S1].总分 &gt;= 17</v>
+        <v>量表[SG_S1].总分 &gt;= 15</v>
       </c>
       <c r="U3" t="str">
-        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
+        <v>五问自评总分达到 15 分及以上（消耗型区间）时建议做深度评估</v>
       </c>
       <c r="V3" t="str">
         <v>teacher_only</v>
@@ -714,13 +714,13 @@
         <v/>
       </c>
       <c r="AA3" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB3" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>状态五问总分达到需支持档位（17 分及以上）时建议做深度评估</v>
+        <v>12 题心理资本（HERO）+3 题依恋安全感快筛（AS）+5 题家长沟通压力（PCS），全部正向计分，得分越低越需关注。</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -755,10 +755,10 @@
         <v>SG_S3</v>
       </c>
       <c r="B4" t="str">
-        <v>教师危机风险自查</v>
+        <v>教师六维深度评估</v>
       </c>
       <c r="C4" t="str">
-        <v>教师危机风险自查</v>
+        <v>六维深评</v>
       </c>
       <c r="D4" t="str">
         <v>self_growth</v>
@@ -788,7 +788,7 @@
         <v>否</v>
       </c>
       <c r="M4" t="str">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -803,16 +803,16 @@
         <v/>
       </c>
       <c r="R4" t="str">
-        <v>SG_S1</v>
+        <v>SG_S2</v>
       </c>
       <c r="S4" t="str">
         <v/>
       </c>
       <c r="T4" t="str">
-        <v>量表[SG_S1].总分 &gt;= 17</v>
+        <v>量表[SG_S2].维度[SG_S2D1] &lt;= 8 或 量表[SG_S2].维度[SG_S2D2] &lt;= 8 或 量表[SG_S2].维度[SG_S2D3] &lt;= 8 或 量表[SG_S2].维度[SG_S2D4] &lt;= 8</v>
       </c>
       <c r="U4" t="str">
-        <v>状态五问总分达到 17 分及以上时，建议做一次危机风险自查</v>
+        <v>HERO 任一维度≤8 分（中度不足）时建议做六维深度评估；也可由顾问判断或学期初制度性安排触发</v>
       </c>
       <c r="V4" t="str">
         <v>teacher_only</v>
@@ -830,13 +830,13 @@
         <v/>
       </c>
       <c r="AA4" t="str">
-        <v>自我成长赋能手册v1</v>
+        <v>个人成长 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB4" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AC4" t="str">
-        <v>状态五问总分达到需支持档位后，逐项自查高危信号，勾选频率越高越需要立即干预。</v>
+        <v>含 MBI-EE 情绪衰竭、PSQI-5 睡眠、HERO 心理资本、BPNSF 基本需要、职业认同、PCS 家长沟通压力 6 个量表共 46 题。六维度各自按阈值分级后取最高预警等级；职业认同&lt;2.5 分触发紫色（意义危机）预警。</v>
       </c>
       <c r="AD4" t="str">
         <v/>
@@ -860,7 +860,7 @@
         <v/>
       </c>
       <c r="AK4" t="str">
-        <v>红线检查</v>
+        <v>深度诊断</v>
       </c>
       <c r="AL4" t="str">
         <v>定位薄弱维度，匹配对应工具</v>
@@ -875,7 +875,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -994,7 +994,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>这一周，我有多少次感到「什么都是我的责任」？</v>
+        <v>这一周，我有多少次感到"什么都是我的责任"？</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -1044,13 +1044,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>这一周，有多少次我觉得「当班主任是值得的」？</v>
+        <v>这一周，有多少次我觉得"当班主任是值得的"？</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>SG_OPT_01</v>
+        <v>FREQ_5</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
@@ -1094,13 +1094,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>遇到让我头疼的学生或家长问题时，我对自己能处理好多有信心？</v>
+        <v>遇到让我头疼的学生或家长问题时，我对自己能处理好有多大信心？</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>FREQ_5</v>
+        <v>SG_OPT_01</v>
       </c>
       <c r="I5" t="str">
         <v>是</v>
@@ -1188,13 +1188,13 @@
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>希望</v>
+        <v>H·职业希望</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>面对当前的班级难题，我能想出不止一条可行的解决路径。</v>
+        <v>我对未来的职业发展有清晰的规划</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -1203,7 +1203,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I7" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J7" t="str">
         <v>1</v>
@@ -1238,13 +1238,13 @@
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>希望</v>
+        <v>H·职业希望</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>我对这个学期想达成的目标有清晰的推进计划。</v>
+        <v>我知道如何成为一个更好的班主任</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -1253,7 +1253,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I8" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J8" t="str">
         <v>1</v>
@@ -1288,13 +1288,13 @@
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>效能信心</v>
+        <v>H·职业希望</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>即使遇到从未处理过的家校冲突，我也相信自己能处理好。</v>
+        <v>即使遇到挫折，我也有多种方法可以实现我的职业目标</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -1303,7 +1303,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I9" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J9" t="str">
         <v>1</v>
@@ -1338,13 +1338,13 @@
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>效能信心</v>
+        <v>E·职业效能</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>我有信心影响班上最难带的那几个学生。</v>
+        <v>我相信自己能够管理好我的班级</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1353,7 +1353,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J10" t="str">
         <v>1</v>
@@ -1388,13 +1388,13 @@
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>韧性</v>
+        <v>E·职业效能</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>被家长质疑或投诉后，我能较快恢复工作状态。</v>
+        <v>我相信我能够与家长建立有效的沟通</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I11" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J11" t="str">
         <v>1</v>
@@ -1438,13 +1438,13 @@
         <v>single</v>
       </c>
       <c r="D12" t="str">
-        <v>韧性</v>
+        <v>E·职业效能</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>工作中的挫折不会长时间影响我的生活。</v>
+        <v>我相信我能够帮助问题学生取得进步</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1453,7 +1453,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I12" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J12" t="str">
         <v>1</v>
@@ -1488,13 +1488,13 @@
         <v>single</v>
       </c>
       <c r="D13" t="str">
-        <v>乐观</v>
+        <v>R·职业韧性</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>我倾向于相信班级的情况会慢慢变好。</v>
+        <v>当学生的问题让我受挫时，我能恢复过来继续工作</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I13" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J13" t="str">
         <v>1</v>
@@ -1538,13 +1538,13 @@
         <v>single</v>
       </c>
       <c r="D14" t="str">
-        <v>乐观</v>
+        <v>R·职业韧性</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>遇到问题时，我更多想到的是机会而不是麻烦。</v>
+        <v>我能从职业挫折中找到成长的资源</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1553,7 +1553,7 @@
         <v>AGREE_5</v>
       </c>
       <c r="I14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J14" t="str">
         <v>1</v>
@@ -1579,28 +1579,28 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SG_S3</v>
+        <v>SG_S2</v>
       </c>
       <c r="B15" t="str">
-        <v>q1</v>
+        <v>q9</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
       </c>
       <c r="D15" t="str">
-        <v>高危信号</v>
+        <v>R·职业韧性</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>最近一周，入睡困难或早醒的情况有多频繁？</v>
+        <v>即使连续遇到困难，我也能坚持做班主任</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I15" t="str">
         <v>否</v>
@@ -1629,28 +1629,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SG_S3</v>
+        <v>SG_S2</v>
       </c>
       <c r="B16" t="str">
-        <v>q2</v>
+        <v>q10</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
       </c>
       <c r="D16" t="str">
-        <v>高危信号</v>
+        <v>O·职业乐观</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>最近一周，上班前感到难以承受、不想面对工作的频率？</v>
+        <v>我的努力通常能带来正面的改变</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I16" t="str">
         <v>否</v>
@@ -1679,28 +1679,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SG_S3</v>
+        <v>SG_S2</v>
       </c>
       <c r="B17" t="str">
-        <v>q3</v>
+        <v>q11</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
       </c>
       <c r="D17" t="str">
-        <v>高危信号</v>
+        <v>O·职业乐观</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>最近一周，出现情绪失控或想对身边人发火的次数？</v>
+        <v>当事情不顺利时，我相信这是可以改变的</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I17" t="str">
         <v>否</v>
@@ -1729,28 +1729,28 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SG_S3</v>
+        <v>SG_S2</v>
       </c>
       <c r="B18" t="str">
-        <v>q4</v>
+        <v>q12</v>
       </c>
       <c r="C18" t="str">
         <v>single</v>
       </c>
       <c r="D18" t="str">
-        <v>高危信号</v>
+        <v>O·职业乐观</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>最近一周，注意力无法集中、做事丢三落四的频率？</v>
+        <v>我相信我正在成为一个更好的老师</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I18" t="str">
         <v>否</v>
@@ -1779,28 +1779,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SG_S3</v>
+        <v>SG_S2</v>
       </c>
       <c r="B19" t="str">
-        <v>q5</v>
+        <v>q13</v>
       </c>
       <c r="C19" t="str">
         <v>single</v>
       </c>
       <c r="D19" t="str">
-        <v>高危信号</v>
+        <v>依恋稳定度</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>最近一周，对工作完全提不起兴趣的频率？</v>
+        <v>当学生向我表达强烈情感需求时，我通常能稳定回应而不会过度卷入或回避</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>FREQ_5</v>
+        <v>SG_OPT_02</v>
       </c>
       <c r="I19" t="str">
         <v>否</v>
@@ -1829,28 +1829,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SG_S3</v>
+        <v>SG_S2</v>
       </c>
       <c r="B20" t="str">
-        <v>q6</v>
+        <v>q14</v>
       </c>
       <c r="C20" t="str">
         <v>single</v>
       </c>
       <c r="D20" t="str">
-        <v>高危信号</v>
+        <v>依恋开放度</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>最近一周，是否出现过伤害自己的念头？</v>
+        <v>面对家长的质疑或不满，我能够在保护自尊的同时保持情感开放</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>FREQ_5</v>
+        <v>SG_OPT_02</v>
       </c>
       <c r="I20" t="str">
         <v>否</v>
@@ -1877,16 +1877,2616 @@
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B21" t="str">
+        <v>q15</v>
+      </c>
+      <c r="C21" t="str">
+        <v>single</v>
+      </c>
+      <c r="D21" t="str">
+        <v>依恋恢复度</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>工作中遇到情感挫折时，我能找到让自己恢复安全感的方式</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>SG_OPT_02</v>
+      </c>
+      <c r="I21" t="str">
+        <v>否</v>
+      </c>
+      <c r="J21" t="str">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>是</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B22" t="str">
+        <v>q16</v>
+      </c>
+      <c r="C22" t="str">
+        <v>single</v>
+      </c>
+      <c r="D22" t="str">
+        <v>时间边界</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>家长随时通过微信/电话联系我，即使在非工作时间，让我感到边界被侵犯</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I22" t="str">
+        <v>否</v>
+      </c>
+      <c r="J22" t="str">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>是</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>q17</v>
+      </c>
+      <c r="C23" t="str">
+        <v>single</v>
+      </c>
+      <c r="D23" t="str">
+        <v>自我怀疑</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>面对家长的质疑或投诉时，我感到委屈、无力，甚至出现自我怀疑</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I23" t="str">
+        <v>否</v>
+      </c>
+      <c r="J23" t="str">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>是</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B24" t="str">
+        <v>q18</v>
+      </c>
+      <c r="C24" t="str">
+        <v>single</v>
+      </c>
+      <c r="D24" t="str">
+        <v>时间消耗</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>需要花费大量时间回复家长群消息、发送通知、解释学校政策，挤占备课和休息时间</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I24" t="str">
+        <v>否</v>
+      </c>
+      <c r="J24" t="str">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>是</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B25" t="str">
+        <v>q19</v>
+      </c>
+      <c r="C25" t="str">
+        <v>single</v>
+      </c>
+      <c r="D25" t="str">
+        <v>过度监督</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>部分家长对学生在校细节过度关注，让我感到被过度监督</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I25" t="str">
+        <v>否</v>
+      </c>
+      <c r="J25" t="str">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>是</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B26" t="str">
+        <v>q20</v>
+      </c>
+      <c r="C26" t="str">
+        <v>single</v>
+      </c>
+      <c r="D26" t="str">
+        <v>协作受阻</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>当学生出现行为问题时，家长倾向于指责教师"管理不到位"，而非共同协作解决</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I26" t="str">
+        <v>否</v>
+      </c>
+      <c r="J26" t="str">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>是</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B27" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>single</v>
+      </c>
+      <c r="D27" t="str">
+        <v>情绪耗竭</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>我的工作让我感到情绪耗竭</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I27" t="str">
+        <v>否</v>
+      </c>
+      <c r="J27" t="str">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>是</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B28" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>single</v>
+      </c>
+      <c r="D28" t="str">
+        <v>精力耗尽</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>下班后我感觉精力完全耗尽</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I28" t="str">
+        <v>否</v>
+      </c>
+      <c r="J28" t="str">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>是</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B29" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C29" t="str">
+        <v>single</v>
+      </c>
+      <c r="D29" t="str">
+        <v>晨起疲惫</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>早上起来想到又要面对一天的工作，我就觉得疲惫不堪</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I29" t="str">
+        <v>否</v>
+      </c>
+      <c r="J29" t="str">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>是</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B30" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C30" t="str">
+        <v>single</v>
+      </c>
+      <c r="D30" t="str">
+        <v>人际压力</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>整天与人打交道让我感到压力很大</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I30" t="str">
+        <v>否</v>
+      </c>
+      <c r="J30" t="str">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>是</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B31" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C31" t="str">
+        <v>single</v>
+      </c>
+      <c r="D31" t="str">
+        <v>身心俱疲</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>我感到自己的工作让我身心俱疲（burned out）</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I31" t="str">
+        <v>否</v>
+      </c>
+      <c r="J31" t="str">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>是</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B32" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C32" t="str">
+        <v>single</v>
+      </c>
+      <c r="D32" t="str">
+        <v>工作挫折</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>工作让我感到挫折</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I32" t="str">
+        <v>否</v>
+      </c>
+      <c r="J32" t="str">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>是</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B33" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C33" t="str">
+        <v>single</v>
+      </c>
+      <c r="D33" t="str">
+        <v>过度努力</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>我觉得自己工作太拼命了</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I33" t="str">
+        <v>否</v>
+      </c>
+      <c r="J33" t="str">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>是</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B34" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C34" t="str">
+        <v>single</v>
+      </c>
+      <c r="D34" t="str">
+        <v>直接压力</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>直接与人打交道让我感到压力很大</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I34" t="str">
+        <v>否</v>
+      </c>
+      <c r="J34" t="str">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>是</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B35" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C35" t="str">
+        <v>single</v>
+      </c>
+      <c r="D35" t="str">
+        <v>到达极限</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>我感到自己已经到了承受的极限</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="I35" t="str">
+        <v>否</v>
+      </c>
+      <c r="J35" t="str">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>是</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B36" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C36" t="str">
+        <v>single</v>
+      </c>
+      <c r="D36" t="str">
+        <v>入睡时间</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>最近1个月，你通常需要多长时间才能入睡？</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>SG_OPT_05</v>
+      </c>
+      <c r="I36" t="str">
+        <v>否</v>
+      </c>
+      <c r="J36" t="str">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>是</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B37" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C37" t="str">
+        <v>single</v>
+      </c>
+      <c r="D37" t="str">
+        <v>睡眠时间</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>最近1个月，你每晚实际睡眠时间大约是？</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>SG_OPT_06</v>
+      </c>
+      <c r="I37" t="str">
+        <v>否</v>
+      </c>
+      <c r="J37" t="str">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>是</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B38" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C38" t="str">
+        <v>single</v>
+      </c>
+      <c r="D38" t="str">
+        <v>睡眠障碍</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>最近1个月，你有以下睡眠问题的频率（夜间易醒/早醒/需要药物助眠等）？</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>SG_OPT_07</v>
+      </c>
+      <c r="I38" t="str">
+        <v>否</v>
+      </c>
+      <c r="J38" t="str">
+        <v>1</v>
+      </c>
+      <c r="K38" t="str">
+        <v>是</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B39" t="str">
+        <v>q13</v>
+      </c>
+      <c r="C39" t="str">
+        <v>single</v>
+      </c>
+      <c r="D39" t="str">
+        <v>睡眠效率</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>最近1个月，你的睡眠效率如何（实际睡眠时间÷卧床时间）？</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>SG_OPT_08</v>
+      </c>
+      <c r="I39" t="str">
+        <v>否</v>
+      </c>
+      <c r="J39" t="str">
+        <v>1</v>
+      </c>
+      <c r="K39" t="str">
+        <v>是</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B40" t="str">
+        <v>q14</v>
+      </c>
+      <c r="C40" t="str">
+        <v>single</v>
+      </c>
+      <c r="D40" t="str">
+        <v>主观质量</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>最近1个月，你对自己的总体睡眠质量评价如何？</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>SG_OPT_09</v>
+      </c>
+      <c r="I40" t="str">
+        <v>否</v>
+      </c>
+      <c r="J40" t="str">
+        <v>1</v>
+      </c>
+      <c r="K40" t="str">
+        <v>是</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B41" t="str">
+        <v>q15</v>
+      </c>
+      <c r="C41" t="str">
+        <v>single</v>
+      </c>
+      <c r="D41" t="str">
+        <v>H·职业希望</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>我对未来的职业发展有清晰的规划</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I41" t="str">
+        <v>否</v>
+      </c>
+      <c r="J41" t="str">
+        <v>1</v>
+      </c>
+      <c r="K41" t="str">
+        <v>是</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B42" t="str">
+        <v>q16</v>
+      </c>
+      <c r="C42" t="str">
+        <v>single</v>
+      </c>
+      <c r="D42" t="str">
+        <v>H·职业希望</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>我知道如何成为一个更好的班主任</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I42" t="str">
+        <v>否</v>
+      </c>
+      <c r="J42" t="str">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>是</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B43" t="str">
+        <v>q17</v>
+      </c>
+      <c r="C43" t="str">
+        <v>single</v>
+      </c>
+      <c r="D43" t="str">
+        <v>H·职业希望</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>即使遇到挫折，我也有多种方法可以实现我的职业目标</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I43" t="str">
+        <v>否</v>
+      </c>
+      <c r="J43" t="str">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>是</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B44" t="str">
+        <v>q18</v>
+      </c>
+      <c r="C44" t="str">
+        <v>single</v>
+      </c>
+      <c r="D44" t="str">
+        <v>E·职业效能</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>我相信自己能够管理好我的班级</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I44" t="str">
+        <v>否</v>
+      </c>
+      <c r="J44" t="str">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>是</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>q19</v>
+      </c>
+      <c r="C45" t="str">
+        <v>single</v>
+      </c>
+      <c r="D45" t="str">
+        <v>E·职业效能</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>我相信我能够与家长建立有效的沟通</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I45" t="str">
+        <v>否</v>
+      </c>
+      <c r="J45" t="str">
+        <v>1</v>
+      </c>
+      <c r="K45" t="str">
+        <v>是</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B46" t="str">
+        <v>q20</v>
+      </c>
+      <c r="C46" t="str">
+        <v>single</v>
+      </c>
+      <c r="D46" t="str">
+        <v>E·职业效能</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>我相信我能够帮助问题学生取得进步</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I46" t="str">
+        <v>否</v>
+      </c>
+      <c r="J46" t="str">
+        <v>1</v>
+      </c>
+      <c r="K46" t="str">
+        <v>是</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B47" t="str">
+        <v>q21</v>
+      </c>
+      <c r="C47" t="str">
+        <v>single</v>
+      </c>
+      <c r="D47" t="str">
+        <v>R·职业韧性</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>当学生的问题让我受挫时，我能恢复过来继续工作</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I47" t="str">
+        <v>否</v>
+      </c>
+      <c r="J47" t="str">
+        <v>1</v>
+      </c>
+      <c r="K47" t="str">
+        <v>是</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B48" t="str">
+        <v>q22</v>
+      </c>
+      <c r="C48" t="str">
+        <v>single</v>
+      </c>
+      <c r="D48" t="str">
+        <v>R·职业韧性</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>我能从职业挫折中找到成长的资源</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I48" t="str">
+        <v>否</v>
+      </c>
+      <c r="J48" t="str">
+        <v>1</v>
+      </c>
+      <c r="K48" t="str">
+        <v>是</v>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B49" t="str">
+        <v>q23</v>
+      </c>
+      <c r="C49" t="str">
+        <v>single</v>
+      </c>
+      <c r="D49" t="str">
+        <v>R·职业韧性</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>即使连续遇到困难，我也能坚持做班主任</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I49" t="str">
+        <v>否</v>
+      </c>
+      <c r="J49" t="str">
+        <v>1</v>
+      </c>
+      <c r="K49" t="str">
+        <v>是</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B50" t="str">
+        <v>q24</v>
+      </c>
+      <c r="C50" t="str">
+        <v>single</v>
+      </c>
+      <c r="D50" t="str">
+        <v>O·职业乐观</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>我的努力通常能带来正面的改变</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I50" t="str">
+        <v>否</v>
+      </c>
+      <c r="J50" t="str">
+        <v>1</v>
+      </c>
+      <c r="K50" t="str">
+        <v>是</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B51" t="str">
+        <v>q25</v>
+      </c>
+      <c r="C51" t="str">
+        <v>single</v>
+      </c>
+      <c r="D51" t="str">
+        <v>O·职业乐观</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>当事情不顺利时，我相信这是可以改变的</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I51" t="str">
+        <v>否</v>
+      </c>
+      <c r="J51" t="str">
+        <v>1</v>
+      </c>
+      <c r="K51" t="str">
+        <v>是</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B52" t="str">
+        <v>q26</v>
+      </c>
+      <c r="C52" t="str">
+        <v>single</v>
+      </c>
+      <c r="D52" t="str">
+        <v>O·职业乐观</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>我相信我正在成为一个更好的老师</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I52" t="str">
+        <v>否</v>
+      </c>
+      <c r="J52" t="str">
+        <v>1</v>
+      </c>
+      <c r="K52" t="str">
+        <v>是</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B53" t="str">
+        <v>q27</v>
+      </c>
+      <c r="C53" t="str">
+        <v>single</v>
+      </c>
+      <c r="D53" t="str">
+        <v>自主需要</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>我在工作中感到有选择的自由</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I53" t="str">
+        <v>否</v>
+      </c>
+      <c r="J53" t="str">
+        <v>1</v>
+      </c>
+      <c r="K53" t="str">
+        <v>是</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B54" t="str">
+        <v>q28</v>
+      </c>
+      <c r="C54" t="str">
+        <v>single</v>
+      </c>
+      <c r="D54" t="str">
+        <v>自主需要</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>我的工作决定能体现真实的自我</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I54" t="str">
+        <v>否</v>
+      </c>
+      <c r="J54" t="str">
+        <v>1</v>
+      </c>
+      <c r="K54" t="str">
+        <v>是</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B55" t="str">
+        <v>q29</v>
+      </c>
+      <c r="C55" t="str">
+        <v>single</v>
+      </c>
+      <c r="D55" t="str">
+        <v>自主需要</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>我在工作中感到自由自主地做事</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I55" t="str">
+        <v>否</v>
+      </c>
+      <c r="J55" t="str">
+        <v>1</v>
+      </c>
+      <c r="K55" t="str">
+        <v>是</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B56" t="str">
+        <v>q30</v>
+      </c>
+      <c r="C56" t="str">
+        <v>single</v>
+      </c>
+      <c r="D56" t="str">
+        <v>能力需要</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>我感到自己有能力完成重要的工作</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I56" t="str">
+        <v>否</v>
+      </c>
+      <c r="J56" t="str">
+        <v>1</v>
+      </c>
+      <c r="K56" t="str">
+        <v>是</v>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B57" t="str">
+        <v>q31</v>
+      </c>
+      <c r="C57" t="str">
+        <v>single</v>
+      </c>
+      <c r="D57" t="str">
+        <v>能力需要</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>我能很好地应对工作中的挑战</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I57" t="str">
+        <v>否</v>
+      </c>
+      <c r="J57" t="str">
+        <v>1</v>
+      </c>
+      <c r="K57" t="str">
+        <v>是</v>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B58" t="str">
+        <v>q32</v>
+      </c>
+      <c r="C58" t="str">
+        <v>single</v>
+      </c>
+      <c r="D58" t="str">
+        <v>能力需要</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>我对自己在工作中完成的事情感到满意</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I58" t="str">
+        <v>否</v>
+      </c>
+      <c r="J58" t="str">
+        <v>1</v>
+      </c>
+      <c r="K58" t="str">
+        <v>是</v>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B59" t="str">
+        <v>q33</v>
+      </c>
+      <c r="C59" t="str">
+        <v>single</v>
+      </c>
+      <c r="D59" t="str">
+        <v>关系需要</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>我感到身边有人关心我</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I59" t="str">
+        <v>否</v>
+      </c>
+      <c r="J59" t="str">
+        <v>1</v>
+      </c>
+      <c r="K59" t="str">
+        <v>是</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B60" t="str">
+        <v>q34</v>
+      </c>
+      <c r="C60" t="str">
+        <v>single</v>
+      </c>
+      <c r="D60" t="str">
+        <v>关系需要</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>我感到与他人关系亲密</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I60" t="str">
+        <v>否</v>
+      </c>
+      <c r="J60" t="str">
+        <v>1</v>
+      </c>
+      <c r="K60" t="str">
+        <v>是</v>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B61" t="str">
+        <v>q35</v>
+      </c>
+      <c r="C61" t="str">
+        <v>single</v>
+      </c>
+      <c r="D61" t="str">
+        <v>关系需要</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>我感到被他人尊重和重视</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="I61" t="str">
+        <v>否</v>
+      </c>
+      <c r="J61" t="str">
+        <v>1</v>
+      </c>
+      <c r="K61" t="str">
+        <v>是</v>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B62" t="str">
+        <v>q36</v>
+      </c>
+      <c r="C62" t="str">
+        <v>single</v>
+      </c>
+      <c r="D62" t="str">
+        <v>价值认同</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>我觉得班主任工作对社会有价值</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I62" t="str">
+        <v>否</v>
+      </c>
+      <c r="J62" t="str">
+        <v>1</v>
+      </c>
+      <c r="K62" t="str">
+        <v>是</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B63" t="str">
+        <v>q37</v>
+      </c>
+      <c r="C63" t="str">
+        <v>single</v>
+      </c>
+      <c r="D63" t="str">
+        <v>再选意愿</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>如果重新选择，我还会选择当班主任</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I63" t="str">
+        <v>否</v>
+      </c>
+      <c r="J63" t="str">
+        <v>1</v>
+      </c>
+      <c r="K63" t="str">
+        <v>是</v>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B64" t="str">
+        <v>q38</v>
+      </c>
+      <c r="C64" t="str">
+        <v>single</v>
+      </c>
+      <c r="D64" t="str">
+        <v>职业自豪</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>作为班主任，我感到自豪</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I64" t="str">
+        <v>否</v>
+      </c>
+      <c r="J64" t="str">
+        <v>1</v>
+      </c>
+      <c r="K64" t="str">
+        <v>是</v>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B65" t="str">
+        <v>q39</v>
+      </c>
+      <c r="C65" t="str">
+        <v>single</v>
+      </c>
+      <c r="D65" t="str">
+        <v>长期意愿</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>我愿意在班主任岗位上长期工作</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I65" t="str">
+        <v>否</v>
+      </c>
+      <c r="J65" t="str">
+        <v>1</v>
+      </c>
+      <c r="K65" t="str">
+        <v>是</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B66" t="str">
+        <v>q40</v>
+      </c>
+      <c r="C66" t="str">
+        <v>single</v>
+      </c>
+      <c r="D66" t="str">
+        <v>自我一致</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>我觉得班主任角色与我的自我认知一致</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I66" t="str">
+        <v>否</v>
+      </c>
+      <c r="J66" t="str">
+        <v>1</v>
+      </c>
+      <c r="K66" t="str">
+        <v>是</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B67" t="str">
+        <v>q41</v>
+      </c>
+      <c r="C67" t="str">
+        <v>single</v>
+      </c>
+      <c r="D67" t="str">
+        <v>价值实现</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>我在班主任工作中能体现自己的教育理念</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I67" t="str">
+        <v>否</v>
+      </c>
+      <c r="J67" t="str">
+        <v>1</v>
+      </c>
+      <c r="K67" t="str">
+        <v>是</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B68" t="str">
+        <v>q42</v>
+      </c>
+      <c r="C68" t="str">
+        <v>single</v>
+      </c>
+      <c r="D68" t="str">
+        <v>时间边界</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>家长随时通过微信/电话联系我，即使在非工作时间，让我感到边界被侵犯</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I68" t="str">
+        <v>否</v>
+      </c>
+      <c r="J68" t="str">
+        <v>1</v>
+      </c>
+      <c r="K68" t="str">
+        <v>是</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B69" t="str">
+        <v>q43</v>
+      </c>
+      <c r="C69" t="str">
+        <v>single</v>
+      </c>
+      <c r="D69" t="str">
+        <v>自我怀疑</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>面对家长的质疑或投诉时，我感到委屈、无力，甚至出现自我怀疑</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I69" t="str">
+        <v>否</v>
+      </c>
+      <c r="J69" t="str">
+        <v>1</v>
+      </c>
+      <c r="K69" t="str">
+        <v>是</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B70" t="str">
+        <v>q44</v>
+      </c>
+      <c r="C70" t="str">
+        <v>single</v>
+      </c>
+      <c r="D70" t="str">
+        <v>时间消耗</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>需要花费大量时间回复家长群消息、发送通知、解释学校政策，挤占备课和休息时间</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I70" t="str">
+        <v>否</v>
+      </c>
+      <c r="J70" t="str">
+        <v>1</v>
+      </c>
+      <c r="K70" t="str">
+        <v>是</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B71" t="str">
+        <v>q45</v>
+      </c>
+      <c r="C71" t="str">
+        <v>single</v>
+      </c>
+      <c r="D71" t="str">
+        <v>过度监督</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>部分家长对学生在校细节过度关注，让我感到被过度监督</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I71" t="str">
+        <v>否</v>
+      </c>
+      <c r="J71" t="str">
+        <v>1</v>
+      </c>
+      <c r="K71" t="str">
+        <v>是</v>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B72" t="str">
+        <v>q46</v>
+      </c>
+      <c r="C72" t="str">
+        <v>single</v>
+      </c>
+      <c r="D72" t="str">
+        <v>协作受阻</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>当学生出现行为问题时，家长倾向于指责教师"管理不到位"，而非共同协作解决</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="I72" t="str">
+        <v>否</v>
+      </c>
+      <c r="J72" t="str">
+        <v>1</v>
+      </c>
+      <c r="K72" t="str">
+        <v>是</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P72"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1980,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>完全没有</v>
+        <v>完全没有信心</v>
       </c>
       <c r="D7" t="str">
         <v>1</v>
@@ -1994,7 +4594,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>偶尔有</v>
+        <v>信心不足</v>
       </c>
       <c r="D8" t="str">
         <v>2</v>
@@ -2008,7 +4608,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>有时有</v>
+        <v>一般</v>
       </c>
       <c r="D9" t="str">
         <v>3</v>
@@ -2022,7 +4622,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="str">
-        <v>经常有</v>
+        <v>比较有信心</v>
       </c>
       <c r="D10" t="str">
         <v>4</v>
@@ -2036,7 +4636,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="str">
-        <v>几乎总是</v>
+        <v>非常有信心</v>
       </c>
       <c r="D11" t="str">
         <v>5</v>
@@ -2112,16 +4712,632 @@
         <v>5</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SG_OPT_02</v>
+      </c>
+      <c r="B17" t="str">
+        <v>1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>几乎不能</v>
+      </c>
+      <c r="D17" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SG_OPT_02</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2</v>
+      </c>
+      <c r="C18" t="str">
+        <v>很少能</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SG_OPT_02</v>
+      </c>
+      <c r="B19" t="str">
+        <v>3</v>
+      </c>
+      <c r="C19" t="str">
+        <v>有时能</v>
+      </c>
+      <c r="D19" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SG_OPT_02</v>
+      </c>
+      <c r="B20" t="str">
+        <v>4</v>
+      </c>
+      <c r="C20" t="str">
+        <v>经常能</v>
+      </c>
+      <c r="D20" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SG_OPT_02</v>
+      </c>
+      <c r="B21" t="str">
+        <v>5</v>
+      </c>
+      <c r="C21" t="str">
+        <v>总是能</v>
+      </c>
+      <c r="D21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="B22" t="str">
+        <v>1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>完全没有</v>
+      </c>
+      <c r="D22" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>有一点</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="B24" t="str">
+        <v>3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>中等</v>
+      </c>
+      <c r="D24" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="B25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>较严重</v>
+      </c>
+      <c r="D25" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SG_OPT_03</v>
+      </c>
+      <c r="B26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>非常严重</v>
+      </c>
+      <c r="D26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="B27" t="str">
+        <v>1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>从不</v>
+      </c>
+      <c r="D27" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>一年几次</v>
+      </c>
+      <c r="D28" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="B29" t="str">
+        <v>3</v>
+      </c>
+      <c r="C29" t="str">
+        <v>每月一次</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="B30" t="str">
+        <v>4</v>
+      </c>
+      <c r="C30" t="str">
+        <v>一月几次</v>
+      </c>
+      <c r="D30" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="B31" t="str">
+        <v>5</v>
+      </c>
+      <c r="C31" t="str">
+        <v>每周一次</v>
+      </c>
+      <c r="D31" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="B32" t="str">
+        <v>6</v>
+      </c>
+      <c r="C32" t="str">
+        <v>一周几次</v>
+      </c>
+      <c r="D32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>SG_OPT_04</v>
+      </c>
+      <c r="B33" t="str">
+        <v>7</v>
+      </c>
+      <c r="C33" t="str">
+        <v>每天</v>
+      </c>
+      <c r="D33" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SG_OPT_05</v>
+      </c>
+      <c r="B34" t="str">
+        <v>1</v>
+      </c>
+      <c r="C34" t="str">
+        <v>15分钟以内</v>
+      </c>
+      <c r="D34" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>SG_OPT_05</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2</v>
+      </c>
+      <c r="C35" t="str">
+        <v>16-30分钟</v>
+      </c>
+      <c r="D35" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>SG_OPT_05</v>
+      </c>
+      <c r="B36" t="str">
+        <v>3</v>
+      </c>
+      <c r="C36" t="str">
+        <v>31-60分钟</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SG_OPT_05</v>
+      </c>
+      <c r="B37" t="str">
+        <v>4</v>
+      </c>
+      <c r="C37" t="str">
+        <v>超过60分钟</v>
+      </c>
+      <c r="D37" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>SG_OPT_06</v>
+      </c>
+      <c r="B38" t="str">
+        <v>1</v>
+      </c>
+      <c r="C38" t="str">
+        <v>超过7小时</v>
+      </c>
+      <c r="D38" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SG_OPT_06</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2</v>
+      </c>
+      <c r="C39" t="str">
+        <v>6-7小时</v>
+      </c>
+      <c r="D39" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SG_OPT_06</v>
+      </c>
+      <c r="B40" t="str">
+        <v>3</v>
+      </c>
+      <c r="C40" t="str">
+        <v>5-6小时</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SG_OPT_06</v>
+      </c>
+      <c r="B41" t="str">
+        <v>4</v>
+      </c>
+      <c r="C41" t="str">
+        <v>不足5小时</v>
+      </c>
+      <c r="D41" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SG_OPT_07</v>
+      </c>
+      <c r="B42" t="str">
+        <v>1</v>
+      </c>
+      <c r="C42" t="str">
+        <v>无</v>
+      </c>
+      <c r="D42" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SG_OPT_07</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2</v>
+      </c>
+      <c r="C43" t="str">
+        <v>每周不到1次</v>
+      </c>
+      <c r="D43" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>SG_OPT_07</v>
+      </c>
+      <c r="B44" t="str">
+        <v>3</v>
+      </c>
+      <c r="C44" t="str">
+        <v>每周1-2次</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>SG_OPT_07</v>
+      </c>
+      <c r="B45" t="str">
+        <v>4</v>
+      </c>
+      <c r="C45" t="str">
+        <v>每周3次及以上</v>
+      </c>
+      <c r="D45" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SG_OPT_08</v>
+      </c>
+      <c r="B46" t="str">
+        <v>1</v>
+      </c>
+      <c r="C46" t="str">
+        <v>超过85%</v>
+      </c>
+      <c r="D46" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SG_OPT_08</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2</v>
+      </c>
+      <c r="C47" t="str">
+        <v>75-84%</v>
+      </c>
+      <c r="D47" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>SG_OPT_08</v>
+      </c>
+      <c r="B48" t="str">
+        <v>3</v>
+      </c>
+      <c r="C48" t="str">
+        <v>65-74%</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>SG_OPT_08</v>
+      </c>
+      <c r="B49" t="str">
+        <v>4</v>
+      </c>
+      <c r="C49" t="str">
+        <v>不足65%</v>
+      </c>
+      <c r="D49" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>SG_OPT_09</v>
+      </c>
+      <c r="B50" t="str">
+        <v>1</v>
+      </c>
+      <c r="C50" t="str">
+        <v>很好</v>
+      </c>
+      <c r="D50" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>SG_OPT_09</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2</v>
+      </c>
+      <c r="C51" t="str">
+        <v>较好</v>
+      </c>
+      <c r="D51" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>SG_OPT_09</v>
+      </c>
+      <c r="B52" t="str">
+        <v>3</v>
+      </c>
+      <c r="C52" t="str">
+        <v>较差</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>SG_OPT_09</v>
+      </c>
+      <c r="B53" t="str">
+        <v>4</v>
+      </c>
+      <c r="C53" t="str">
+        <v>很差</v>
+      </c>
+      <c r="D53" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="B54" t="str">
+        <v>1</v>
+      </c>
+      <c r="C54" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D54" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2</v>
+      </c>
+      <c r="C55" t="str">
+        <v>不符合</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="B56" t="str">
+        <v>3</v>
+      </c>
+      <c r="C56" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D56" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="B57" t="str">
+        <v>4</v>
+      </c>
+      <c r="C57" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D57" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="B58" t="str">
+        <v>5</v>
+      </c>
+      <c r="C58" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D58" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="B59" t="str">
+        <v>6</v>
+      </c>
+      <c r="C59" t="str">
+        <v>符合</v>
+      </c>
+      <c r="D59" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>SG_OPT_10</v>
+      </c>
+      <c r="B60" t="str">
+        <v>7</v>
+      </c>
+      <c r="C60" t="str">
+        <v>完全符合</v>
+      </c>
+      <c r="D60" t="str">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D60"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2178,13 +5394,13 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>情绪状态维度</v>
+        <v>身心疲惫难以恢复的频率</v>
       </c>
       <c r="H2" t="str">
-        <v>情绪耗竭风险高，可能伴随躯体症状</v>
+        <v>情绪耗竭风险高</v>
       </c>
       <c r="I2" t="str">
-        <v>情绪状态良好，具备较好的自我调节能力</v>
+        <v>情绪状态良好</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -2213,10 +5429,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>角色边界维度</v>
+        <v>「什么都是我的责任」的频率</v>
       </c>
       <c r="H3" t="str">
-        <v>责任边界模糊，倾向于独自承接全部问题</v>
+        <v>责任边界模糊，独自承接全部问题</v>
       </c>
       <c r="I3" t="str">
         <v>职责边界清晰</v>
@@ -2248,10 +5464,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>意义感知维度</v>
+        <v>「当班主任是值得的」的频率（反向计分）</v>
       </c>
       <c r="H4" t="str">
-        <v>意义感流失，需重点关注</v>
+        <v>意义感流失（转换分高）</v>
       </c>
       <c r="I4" t="str">
         <v>意义感充足</v>
@@ -2283,10 +5499,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>效能信心维度</v>
+        <v>处理棘手问题的信心（反向计分）</v>
       </c>
       <c r="H5" t="str">
-        <v>对处理复杂问题缺乏信心</v>
+        <v>效能信心不足（转换分高）</v>
       </c>
       <c r="I5" t="str">
         <v>效能感稳定</v>
@@ -2318,10 +5534,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>同伴支持维度</v>
+        <v>困难无人分担的频率</v>
       </c>
       <c r="H6" t="str">
-        <v>困难长期无人分担</v>
+        <v>支持来源长期缺失</v>
       </c>
       <c r="I6" t="str">
         <v>有稳定的支持来源</v>
@@ -2341,19 +5557,19 @@
         <v>SG_S2D1</v>
       </c>
       <c r="C7" t="str">
-        <v>希望</v>
+        <v>H·职业希望</v>
       </c>
       <c r="D7" t="str">
-        <v>q1,q2</v>
+        <v>q1,q2,q3</v>
       </c>
       <c r="E7" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F7" t="str">
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>希望维度</v>
+        <v>职业希望，3 题之和 3-15 分</v>
       </c>
       <c r="H7" t="str">
         <v>对目标路径有清晰规划</v>
@@ -2376,19 +5592,19 @@
         <v>SG_S2D2</v>
       </c>
       <c r="C8" t="str">
-        <v>效能信心</v>
+        <v>E·职业效能</v>
       </c>
       <c r="D8" t="str">
-        <v>q3,q4</v>
+        <v>q4,q5,q6</v>
       </c>
       <c r="E8" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F8" t="str">
         <v>1</v>
       </c>
       <c r="G8" t="str">
-        <v>效能信心维度</v>
+        <v>职业效能，3 题之和 3-15 分</v>
       </c>
       <c r="H8" t="str">
         <v>相信自己能应对挑战</v>
@@ -2411,19 +5627,19 @@
         <v>SG_S2D3</v>
       </c>
       <c r="C9" t="str">
-        <v>韧性</v>
+        <v>R·职业韧性</v>
       </c>
       <c r="D9" t="str">
-        <v>q5,q6</v>
+        <v>q7,q8,q9</v>
       </c>
       <c r="E9" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F9" t="str">
         <v>1</v>
       </c>
       <c r="G9" t="str">
-        <v>韧性维度</v>
+        <v>职业韧性，3 题之和 3-15 分</v>
       </c>
       <c r="H9" t="str">
         <v>受挫后能较快恢复</v>
@@ -2446,19 +5662,19 @@
         <v>SG_S2D4</v>
       </c>
       <c r="C10" t="str">
-        <v>乐观</v>
+        <v>O·职业乐观</v>
       </c>
       <c r="D10" t="str">
-        <v>q7,q8</v>
+        <v>q10,q11,q12</v>
       </c>
       <c r="E10" t="str">
-        <v>mean</v>
+        <v>sum</v>
       </c>
       <c r="F10" t="str">
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>乐观维度</v>
+        <v>职业乐观，3 题之和 3-15 分</v>
       </c>
       <c r="H10" t="str">
         <v>对未来持积极预期</v>
@@ -2475,16 +5691,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG_S3</v>
+        <v>SG_S2</v>
       </c>
       <c r="B11" t="str">
-        <v>SG_S3D1</v>
+        <v>SG_S2D5</v>
       </c>
       <c r="C11" t="str">
-        <v>高危信号</v>
+        <v>依恋稳定度</v>
       </c>
       <c r="D11" t="str">
-        <v>q1,q2,q3,q4,q5,q6</v>
+        <v>q13</v>
       </c>
       <c r="E11" t="str">
         <v>mean</v>
@@ -2493,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>面对学生强烈情感需求时能否稳定回应</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -2505,12 +5721,1377 @@
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B12" t="str">
+        <v>SG_S2D6</v>
+      </c>
+      <c r="C12" t="str">
+        <v>依恋开放度</v>
+      </c>
+      <c r="D12" t="str">
+        <v>q14</v>
+      </c>
+      <c r="E12" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F12" t="str">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>面对家长质疑时能否保护自尊同时保持情感开放</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SG_S2D7</v>
+      </c>
+      <c r="C13" t="str">
+        <v>依恋恢复度</v>
+      </c>
+      <c r="D13" t="str">
+        <v>q15</v>
+      </c>
+      <c r="E13" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F13" t="str">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>情感挫折后能否找到恢复安全感的方式</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B14" t="str">
+        <v>SG_S2D8</v>
+      </c>
+      <c r="C14" t="str">
+        <v>时间边界</v>
+      </c>
+      <c r="D14" t="str">
+        <v>q16</v>
+      </c>
+      <c r="E14" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F14" t="str">
+        <v>1</v>
+      </c>
+      <c r="G14" t="str">
+        <v>非工作时间被联系时的边界侵犯感</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>SG_S2D9</v>
+      </c>
+      <c r="C15" t="str">
+        <v>自我怀疑</v>
+      </c>
+      <c r="D15" t="str">
+        <v>q17</v>
+      </c>
+      <c r="E15" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F15" t="str">
+        <v>1</v>
+      </c>
+      <c r="G15" t="str">
+        <v>面对质疑投诉时的委屈无力与自我怀疑</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B16" t="str">
+        <v>SG_S2D10</v>
+      </c>
+      <c r="C16" t="str">
+        <v>时间消耗</v>
+      </c>
+      <c r="D16" t="str">
+        <v>q18</v>
+      </c>
+      <c r="E16" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F16" t="str">
+        <v>1</v>
+      </c>
+      <c r="G16" t="str">
+        <v>家长沟通挤占备课与休息时间的程度</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>SG_S2D11</v>
+      </c>
+      <c r="C17" t="str">
+        <v>过度监督</v>
+      </c>
+      <c r="D17" t="str">
+        <v>q19</v>
+      </c>
+      <c r="E17" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F17" t="str">
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
+        <v>被家长过度监督的感受</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SG_S2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>SG_S2D12</v>
+      </c>
+      <c r="C18" t="str">
+        <v>协作受阻</v>
+      </c>
+      <c r="D18" t="str">
+        <v>q20</v>
+      </c>
+      <c r="E18" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F18" t="str">
+        <v>1</v>
+      </c>
+      <c r="G18" t="str">
+        <v>家长指责教师管理不到位的程度</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>SG_S3D1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>情绪耗竭</v>
+      </c>
+      <c r="D19" t="str">
+        <v>q1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SG_S3D2</v>
+      </c>
+      <c r="C20" t="str">
+        <v>精力耗尽</v>
+      </c>
+      <c r="D20" t="str">
+        <v>q2</v>
+      </c>
+      <c r="E20" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SG_S3D3</v>
+      </c>
+      <c r="C21" t="str">
+        <v>晨起疲惫</v>
+      </c>
+      <c r="D21" t="str">
+        <v>q3</v>
+      </c>
+      <c r="E21" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SG_S3D4</v>
+      </c>
+      <c r="C22" t="str">
+        <v>人际压力</v>
+      </c>
+      <c r="D22" t="str">
+        <v>q4</v>
+      </c>
+      <c r="E22" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B23" t="str">
+        <v>SG_S3D5</v>
+      </c>
+      <c r="C23" t="str">
+        <v>身心俱疲</v>
+      </c>
+      <c r="D23" t="str">
+        <v>q5</v>
+      </c>
+      <c r="E23" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SG_S3D6</v>
+      </c>
+      <c r="C24" t="str">
+        <v>工作挫折</v>
+      </c>
+      <c r="D24" t="str">
+        <v>q6</v>
+      </c>
+      <c r="E24" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B25" t="str">
+        <v>SG_S3D7</v>
+      </c>
+      <c r="C25" t="str">
+        <v>过度努力</v>
+      </c>
+      <c r="D25" t="str">
+        <v>q7</v>
+      </c>
+      <c r="E25" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SG_S3D8</v>
+      </c>
+      <c r="C26" t="str">
+        <v>直接压力</v>
+      </c>
+      <c r="D26" t="str">
+        <v>q8</v>
+      </c>
+      <c r="E26" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SG_S3D9</v>
+      </c>
+      <c r="C27" t="str">
+        <v>到达极限</v>
+      </c>
+      <c r="D27" t="str">
+        <v>q9</v>
+      </c>
+      <c r="E27" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SG_S3D10</v>
+      </c>
+      <c r="C28" t="str">
+        <v>入睡时间</v>
+      </c>
+      <c r="D28" t="str">
+        <v>q10</v>
+      </c>
+      <c r="E28" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F28" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B29" t="str">
+        <v>SG_S3D11</v>
+      </c>
+      <c r="C29" t="str">
+        <v>睡眠时间</v>
+      </c>
+      <c r="D29" t="str">
+        <v>q11</v>
+      </c>
+      <c r="E29" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F29" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B30" t="str">
+        <v>SG_S3D12</v>
+      </c>
+      <c r="C30" t="str">
+        <v>睡眠障碍</v>
+      </c>
+      <c r="D30" t="str">
+        <v>q12</v>
+      </c>
+      <c r="E30" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F30" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B31" t="str">
+        <v>SG_S3D13</v>
+      </c>
+      <c r="C31" t="str">
+        <v>睡眠效率</v>
+      </c>
+      <c r="D31" t="str">
+        <v>q13</v>
+      </c>
+      <c r="E31" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F31" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B32" t="str">
+        <v>SG_S3D14</v>
+      </c>
+      <c r="C32" t="str">
+        <v>主观质量</v>
+      </c>
+      <c r="D32" t="str">
+        <v>q14</v>
+      </c>
+      <c r="E32" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F32" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B33" t="str">
+        <v>SG_S3D15</v>
+      </c>
+      <c r="C33" t="str">
+        <v>H·职业希望</v>
+      </c>
+      <c r="D33" t="str">
+        <v>q15,q16,q17</v>
+      </c>
+      <c r="E33" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F33" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B34" t="str">
+        <v>SG_S3D16</v>
+      </c>
+      <c r="C34" t="str">
+        <v>E·职业效能</v>
+      </c>
+      <c r="D34" t="str">
+        <v>q18,q19,q20</v>
+      </c>
+      <c r="E34" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F34" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B35" t="str">
+        <v>SG_S3D17</v>
+      </c>
+      <c r="C35" t="str">
+        <v>R·职业韧性</v>
+      </c>
+      <c r="D35" t="str">
+        <v>q21,q22,q23</v>
+      </c>
+      <c r="E35" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F35" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B36" t="str">
+        <v>SG_S3D18</v>
+      </c>
+      <c r="C36" t="str">
+        <v>O·职业乐观</v>
+      </c>
+      <c r="D36" t="str">
+        <v>q24,q25,q26</v>
+      </c>
+      <c r="E36" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F36" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B37" t="str">
+        <v>SG_S3D19</v>
+      </c>
+      <c r="C37" t="str">
+        <v>自主需要</v>
+      </c>
+      <c r="D37" t="str">
+        <v>q27,q28,q29</v>
+      </c>
+      <c r="E37" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F37" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B38" t="str">
+        <v>SG_S3D20</v>
+      </c>
+      <c r="C38" t="str">
+        <v>能力需要</v>
+      </c>
+      <c r="D38" t="str">
+        <v>q30,q31,q32</v>
+      </c>
+      <c r="E38" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F38" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B39" t="str">
+        <v>SG_S3D21</v>
+      </c>
+      <c r="C39" t="str">
+        <v>关系需要</v>
+      </c>
+      <c r="D39" t="str">
+        <v>q33,q34,q35</v>
+      </c>
+      <c r="E39" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F39" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B40" t="str">
+        <v>SG_S3D22</v>
+      </c>
+      <c r="C40" t="str">
+        <v>价值认同</v>
+      </c>
+      <c r="D40" t="str">
+        <v>q36</v>
+      </c>
+      <c r="E40" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F40" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B41" t="str">
+        <v>SG_S3D23</v>
+      </c>
+      <c r="C41" t="str">
+        <v>再选意愿</v>
+      </c>
+      <c r="D41" t="str">
+        <v>q37</v>
+      </c>
+      <c r="E41" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F41" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B42" t="str">
+        <v>SG_S3D24</v>
+      </c>
+      <c r="C42" t="str">
+        <v>职业自豪</v>
+      </c>
+      <c r="D42" t="str">
+        <v>q38</v>
+      </c>
+      <c r="E42" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F42" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B43" t="str">
+        <v>SG_S3D25</v>
+      </c>
+      <c r="C43" t="str">
+        <v>长期意愿</v>
+      </c>
+      <c r="D43" t="str">
+        <v>q39</v>
+      </c>
+      <c r="E43" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F43" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B44" t="str">
+        <v>SG_S3D26</v>
+      </c>
+      <c r="C44" t="str">
+        <v>自我一致</v>
+      </c>
+      <c r="D44" t="str">
+        <v>q40</v>
+      </c>
+      <c r="E44" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F44" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>SG_S3D27</v>
+      </c>
+      <c r="C45" t="str">
+        <v>价值实现</v>
+      </c>
+      <c r="D45" t="str">
+        <v>q41</v>
+      </c>
+      <c r="E45" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F45" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B46" t="str">
+        <v>SG_S3D28</v>
+      </c>
+      <c r="C46" t="str">
+        <v>时间边界</v>
+      </c>
+      <c r="D46" t="str">
+        <v>q42</v>
+      </c>
+      <c r="E46" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F46" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B47" t="str">
+        <v>SG_S3D29</v>
+      </c>
+      <c r="C47" t="str">
+        <v>自我怀疑</v>
+      </c>
+      <c r="D47" t="str">
+        <v>q43</v>
+      </c>
+      <c r="E47" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F47" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B48" t="str">
+        <v>SG_S3D30</v>
+      </c>
+      <c r="C48" t="str">
+        <v>时间消耗</v>
+      </c>
+      <c r="D48" t="str">
+        <v>q44</v>
+      </c>
+      <c r="E48" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F48" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B49" t="str">
+        <v>SG_S3D31</v>
+      </c>
+      <c r="C49" t="str">
+        <v>过度监督</v>
+      </c>
+      <c r="D49" t="str">
+        <v>q45</v>
+      </c>
+      <c r="E49" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F49" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>SG_S3</v>
+      </c>
+      <c r="B50" t="str">
+        <v>SG_S3D32</v>
+      </c>
+      <c r="C50" t="str">
+        <v>协作受阻</v>
+      </c>
+      <c r="D50" t="str">
+        <v>q46</v>
+      </c>
+      <c r="E50" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F50" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>